--- a/uploads/excels/LIMS_Test_Pvt_land_Data_format_24.03.26_(1)_(3).xlsx
+++ b/uploads/excels/LIMS_Test_Pvt_land_Data_format_24.03.26_(1)_(3).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\lims up file format\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44624FDB-975B-4FB6-9E0E-AF07BC26E06C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32C9AD76-D471-42A2-86E4-2108360E8543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$1:$CI$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$1:$CK$32</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="308">
   <si>
     <t>SES Survey No.</t>
   </si>
@@ -128,9 +128,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve"> Total Value  (Land-22 + Tree-24 + House-26 + Structures-28)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Solatium @ of (100%) </t>
   </si>
   <si>
@@ -938,12 +935,6 @@
     <t>demand of higher compensation</t>
   </si>
   <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
     <t>Full/Part</t>
   </si>
   <si>
@@ -951,6 +942,27 @@
   </si>
   <si>
     <t>Part</t>
+  </si>
+  <si>
+    <t>Total Value  (Land-22 + Tree-24 + House-26 + Structures-28)</t>
+  </si>
+  <si>
+    <t>No. of days of Interest</t>
+  </si>
+  <si>
+    <t>District</t>
+  </si>
+  <si>
+    <t>Angul</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Electrician</t>
   </si>
 </sst>
 </file>
@@ -1597,7 +1609,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CI35"/>
+  <dimension ref="A1:CK35"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="8"/>
@@ -1606,66 +1618,67 @@
     <col min="4" max="4" width="31.5703125" style="8" customWidth="1"/>
     <col min="5" max="5" width="25.85546875" style="8" customWidth="1"/>
     <col min="6" max="6" width="29.42578125" style="8" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="8"/>
-    <col min="8" max="8" width="20.140625" style="8" customWidth="1"/>
-    <col min="9" max="10" width="17.5703125" style="8" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="8" customWidth="1"/>
-    <col min="12" max="12" width="12" style="8" customWidth="1"/>
-    <col min="13" max="13" width="17.28515625" style="8" customWidth="1"/>
-    <col min="14" max="14" width="12.42578125" style="8" customWidth="1"/>
-    <col min="15" max="19" width="9.140625" style="8"/>
-    <col min="20" max="20" width="13.28515625" style="8" customWidth="1"/>
-    <col min="21" max="21" width="9.140625" style="8"/>
-    <col min="22" max="22" width="12.28515625" style="8" customWidth="1"/>
-    <col min="23" max="23" width="13.7109375" style="8" customWidth="1"/>
-    <col min="24" max="24" width="12.28515625" style="8" customWidth="1"/>
-    <col min="25" max="25" width="16" style="8" customWidth="1"/>
-    <col min="26" max="26" width="12.42578125" style="8" customWidth="1"/>
-    <col min="27" max="27" width="9.140625" style="8"/>
-    <col min="28" max="28" width="13.42578125" style="8" customWidth="1"/>
-    <col min="29" max="29" width="9.140625" style="8"/>
-    <col min="30" max="30" width="9.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12" style="8" customWidth="1"/>
-    <col min="32" max="32" width="12.7109375" style="8" customWidth="1"/>
-    <col min="33" max="33" width="13" style="8" customWidth="1"/>
-    <col min="34" max="34" width="17.5703125" style="8" customWidth="1"/>
-    <col min="35" max="35" width="10.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13" style="8" customWidth="1"/>
-    <col min="37" max="37" width="15.85546875" style="8" customWidth="1"/>
-    <col min="38" max="38" width="9.140625" style="8"/>
-    <col min="39" max="39" width="15.7109375" style="8" customWidth="1"/>
-    <col min="40" max="40" width="18.85546875" style="8" customWidth="1"/>
-    <col min="41" max="41" width="12.7109375" style="8" customWidth="1"/>
-    <col min="42" max="42" width="17.85546875" style="8" customWidth="1"/>
-    <col min="43" max="43" width="20" style="8" customWidth="1"/>
-    <col min="44" max="44" width="9.140625" style="8"/>
-    <col min="45" max="45" width="14.140625" style="8" customWidth="1"/>
-    <col min="46" max="46" width="10.7109375" style="8" customWidth="1"/>
-    <col min="47" max="47" width="16.140625" style="8" customWidth="1"/>
-    <col min="48" max="48" width="14.140625" style="8" customWidth="1"/>
-    <col min="49" max="50" width="9.140625" style="8"/>
-    <col min="51" max="51" width="22.28515625" style="8" customWidth="1"/>
-    <col min="52" max="59" width="9.140625" style="8"/>
-    <col min="60" max="60" width="19.7109375" style="8" customWidth="1"/>
-    <col min="61" max="61" width="9.140625" style="8"/>
-    <col min="62" max="62" width="10.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="21.28515625" style="8" customWidth="1"/>
-    <col min="64" max="64" width="16" style="8" customWidth="1"/>
-    <col min="65" max="65" width="27" style="8" customWidth="1"/>
-    <col min="66" max="66" width="11.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="67" max="70" width="9.140625" style="8"/>
-    <col min="71" max="76" width="11.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="77" max="80" width="9.140625" style="8"/>
-    <col min="81" max="81" width="10.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="82" max="82" width="16" style="8" customWidth="1"/>
-    <col min="83" max="83" width="9.140625" style="8"/>
-    <col min="84" max="84" width="19.85546875" style="8" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="8"/>
+    <col min="9" max="9" width="20.140625" style="8" customWidth="1"/>
+    <col min="10" max="11" width="17.5703125" style="8" customWidth="1"/>
+    <col min="12" max="12" width="15.7109375" style="8" customWidth="1"/>
+    <col min="13" max="13" width="12" style="8" customWidth="1"/>
+    <col min="14" max="14" width="17.28515625" style="8" customWidth="1"/>
+    <col min="15" max="15" width="12.42578125" style="8" customWidth="1"/>
+    <col min="16" max="20" width="9.140625" style="8"/>
+    <col min="21" max="21" width="13.28515625" style="8" customWidth="1"/>
+    <col min="22" max="22" width="9.140625" style="8"/>
+    <col min="23" max="23" width="12.28515625" style="8" customWidth="1"/>
+    <col min="24" max="24" width="13.7109375" style="8" customWidth="1"/>
+    <col min="25" max="25" width="12.28515625" style="8" customWidth="1"/>
+    <col min="26" max="26" width="16" style="8" customWidth="1"/>
+    <col min="27" max="27" width="12.42578125" style="8" customWidth="1"/>
+    <col min="28" max="28" width="9.140625" style="8"/>
+    <col min="29" max="29" width="13.42578125" style="8" customWidth="1"/>
+    <col min="30" max="30" width="9.140625" style="8"/>
+    <col min="31" max="31" width="9.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12" style="8" customWidth="1"/>
+    <col min="33" max="34" width="12.7109375" style="8" customWidth="1"/>
+    <col min="35" max="35" width="13" style="8" customWidth="1"/>
+    <col min="36" max="36" width="17.5703125" style="8" customWidth="1"/>
+    <col min="37" max="37" width="10.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13" style="8" customWidth="1"/>
+    <col min="39" max="39" width="15.85546875" style="8" customWidth="1"/>
+    <col min="40" max="40" width="9.140625" style="8"/>
+    <col min="41" max="41" width="15.7109375" style="8" customWidth="1"/>
+    <col min="42" max="42" width="18.85546875" style="8" customWidth="1"/>
+    <col min="43" max="43" width="12.7109375" style="8" customWidth="1"/>
+    <col min="44" max="44" width="17.85546875" style="8" customWidth="1"/>
+    <col min="45" max="45" width="20" style="8" customWidth="1"/>
+    <col min="46" max="46" width="9.140625" style="8"/>
+    <col min="47" max="47" width="14.140625" style="8" customWidth="1"/>
+    <col min="48" max="48" width="10.7109375" style="8" customWidth="1"/>
+    <col min="49" max="49" width="16.140625" style="8" customWidth="1"/>
+    <col min="50" max="50" width="14.140625" style="8" customWidth="1"/>
+    <col min="51" max="51" width="9.140625" style="8"/>
+    <col min="52" max="52" width="14.42578125" style="8" customWidth="1"/>
+    <col min="53" max="53" width="22.28515625" style="8" customWidth="1"/>
+    <col min="54" max="61" width="9.140625" style="8"/>
+    <col min="62" max="62" width="19.7109375" style="8" customWidth="1"/>
+    <col min="63" max="63" width="9.140625" style="8"/>
+    <col min="64" max="64" width="10.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="21.28515625" style="8" customWidth="1"/>
+    <col min="66" max="66" width="16" style="8" customWidth="1"/>
+    <col min="67" max="67" width="27" style="8" customWidth="1"/>
+    <col min="68" max="68" width="11.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="69" max="72" width="9.140625" style="8"/>
+    <col min="73" max="78" width="11.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="79" max="82" width="9.140625" style="8"/>
+    <col min="83" max="83" width="10.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="16" style="8" customWidth="1"/>
     <col min="85" max="85" width="9.140625" style="8"/>
-    <col min="86" max="86" width="10.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="87" max="16384" width="9.140625" style="8"/>
+    <col min="86" max="86" width="19.85546875" style="8" customWidth="1"/>
+    <col min="87" max="87" width="9.140625" style="8"/>
+    <col min="88" max="88" width="10.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="89" max="16384" width="9.140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:87" ht="82.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:89" ht="82.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1688,1548 +1701,1577 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF1" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="R1" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S1" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="T1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="U1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="AI1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AO1" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="AM1" s="5" t="s">
+      <c r="AP1" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="AN1" s="5" t="s">
+      <c r="AQ1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="AO1" s="3" t="s">
+      <c r="AR1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AP1" s="3" t="s">
+      <c r="AS1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AQ1" s="3" t="s">
+      <c r="AT1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AR1" s="3" t="s">
+      <c r="AU1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AS1" s="3" t="s">
+      <c r="AV1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="AT1" s="3" t="s">
+      <c r="AW1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="AU1" s="3" t="s">
+      <c r="AX1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="AV1" s="3" t="s">
+      <c r="AY1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AW1" s="3" t="s">
+      <c r="AZ1" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AX1" s="3" t="s">
+      <c r="BA1" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="AY1" s="3" t="s">
+      <c r="BB1" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AZ1" s="3" t="s">
+      <c r="BC1" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="BA1" s="3" t="s">
+      <c r="BD1" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="BB1" s="3" t="s">
+      <c r="BE1" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="BC1" s="3" t="s">
+      <c r="BF1" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="BD1" s="3" t="s">
+      <c r="BG1" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="BE1" s="3" t="s">
+      <c r="BH1" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="BF1" s="3" t="s">
+      <c r="BI1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="BG1" s="3" t="s">
+      <c r="BJ1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="BH1" s="3" t="s">
+      <c r="BK1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="BI1" s="3" t="s">
+      <c r="BL1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="BJ1" s="3" t="s">
+      <c r="BM1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="BK1" s="3" t="s">
+      <c r="BN1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="BL1" s="3" t="s">
+      <c r="BO1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="BM1" s="3" t="s">
+      <c r="BP1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="BN1" s="3" t="s">
+      <c r="BQ1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="BO1" s="3" t="s">
+      <c r="BR1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="BP1" s="3" t="s">
+      <c r="BS1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="BQ1" s="3" t="s">
+      <c r="BT1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="BR1" s="3" t="s">
+      <c r="BU1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="BS1" s="3" t="s">
+      <c r="BV1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="BT1" s="3" t="s">
+      <c r="BW1" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="BU1" s="3" t="s">
+      <c r="BX1" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="BV1" s="3" t="s">
+      <c r="BY1" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="BW1" s="3" t="s">
+      <c r="BZ1" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="BX1" s="3" t="s">
+      <c r="CA1" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="BY1" s="3" t="s">
+      <c r="CB1" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="BZ1" s="3" t="s">
+      <c r="CC1" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="CA1" s="3" t="s">
+      <c r="CD1" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="CB1" s="3" t="s">
+      <c r="CE1" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="CC1" s="3" t="s">
+      <c r="CF1" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="CD1" s="3" t="s">
+      <c r="CG1" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="CE1" s="3" t="s">
+      <c r="CH1" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="CF1" s="3" t="s">
+      <c r="CI1" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="CG1" s="3" t="s">
+      <c r="CJ1" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="CH1" s="3" t="s">
+      <c r="CK1" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="CI1" s="3" t="s">
-        <v>85</v>
-      </c>
     </row>
-    <row r="2" spans="1:87" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:89" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8">
         <v>1</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C2" s="31">
         <v>46100</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F2" s="47" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="H2" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="L2" s="11">
+        <v>76</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="N2" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I2" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="J2" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="K2" s="11">
-        <v>76</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M2" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="N2" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="O2" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="P2" s="45" t="s">
-        <v>298</v>
-      </c>
-      <c r="Q2" s="38" t="s">
-        <v>302</v>
-      </c>
-      <c r="R2" s="15">
+      <c r="O2" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="P2" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q2" s="45" t="s">
+        <v>297</v>
+      </c>
+      <c r="R2" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="S2" s="15">
         <v>0.02</v>
       </c>
-      <c r="S2" s="15">
+      <c r="T2" s="15">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="T2" s="15">
+      <c r="U2" s="15">
         <v>0.02</v>
       </c>
-      <c r="U2" s="15">
+      <c r="V2" s="15">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="V2" s="7">
+      <c r="W2" s="7">
         <v>2951781</v>
       </c>
-      <c r="W2" s="16" t="s">
-        <v>244</v>
-      </c>
-      <c r="X2" s="33">
+      <c r="X2" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Y2" s="33">
         <v>118072</v>
       </c>
-      <c r="Y2" s="38">
+      <c r="Z2" s="38">
         <v>15</v>
       </c>
-      <c r="Z2" s="32">
+      <c r="AA2" s="32">
         <v>9944</v>
       </c>
-      <c r="AA2" s="38">
+      <c r="AB2" s="38">
         <v>21</v>
       </c>
-      <c r="AB2" s="32">
+      <c r="AC2" s="32">
         <v>1318174</v>
       </c>
-      <c r="AC2" s="38">
+      <c r="AD2" s="38">
         <v>3</v>
       </c>
-      <c r="AD2" s="32">
-        <v>0</v>
-      </c>
       <c r="AE2" s="32">
-        <v>1436246</v>
+        <v>0</v>
       </c>
       <c r="AF2" s="32">
         <v>1436246</v>
       </c>
       <c r="AG2" s="32">
+        <v>1436246</v>
+      </c>
+      <c r="AH2" s="32">
+        <v>10</v>
+      </c>
+      <c r="AI2" s="32">
         <v>16575</v>
       </c>
-      <c r="AH2" s="32">
+      <c r="AJ2" s="32">
         <v>2889067</v>
       </c>
-      <c r="AI2" s="32">
+      <c r="AK2" s="32">
         <v>2889067</v>
       </c>
-      <c r="AJ2" s="23" t="s">
-        <v>287</v>
-      </c>
-      <c r="AK2" s="23" t="s">
-        <v>290</v>
-      </c>
-      <c r="AL2" s="27" t="s">
-        <v>294</v>
-      </c>
-      <c r="AM2" s="18" t="s">
+      <c r="AL2" s="23" t="s">
+        <v>286</v>
+      </c>
+      <c r="AM2" s="23" t="s">
+        <v>289</v>
+      </c>
+      <c r="AN2" s="27" t="s">
+        <v>293</v>
+      </c>
+      <c r="AO2" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="AP2" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="AN2" s="19" t="s">
+      <c r="AQ2" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="AO2" s="19" t="s">
+      <c r="AR2" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="AP2" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="AQ2" s="37" t="s">
-        <v>245</v>
-      </c>
-      <c r="AR2" s="37">
+      <c r="AS2" s="37" t="s">
+        <v>244</v>
+      </c>
+      <c r="AT2" s="37">
         <v>36</v>
       </c>
-      <c r="AS2" t="s">
-        <v>257</v>
-      </c>
-      <c r="AT2" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="AU2" s="8" t="s">
-        <v>273</v>
+      <c r="AU2" t="s">
+        <v>256</v>
       </c>
       <c r="AV2" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="AW2" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="AW2" s="8">
+      <c r="AX2" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="AY2" s="8">
         <v>130000</v>
       </c>
-      <c r="AY2" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="AZ2" s="11">
-        <v>1</v>
-      </c>
-      <c r="BA2" s="11">
-        <v>1</v>
+      <c r="BA2" s="8" t="s">
+        <v>274</v>
       </c>
       <c r="BB2" s="11">
         <v>1</v>
       </c>
       <c r="BC2" s="11">
+        <v>1</v>
+      </c>
+      <c r="BD2" s="11">
+        <v>1</v>
+      </c>
+      <c r="BE2" s="11">
         <v>2</v>
       </c>
-      <c r="BD2" s="11">
-        <v>0</v>
-      </c>
-      <c r="BE2" s="11">
-        <v>0</v>
-      </c>
       <c r="BF2" s="11">
         <v>0</v>
       </c>
       <c r="BG2" s="11">
         <v>0</v>
       </c>
-      <c r="BI2" s="39" t="s">
-        <v>111</v>
-      </c>
-      <c r="BJ2" s="42">
+      <c r="BH2" s="11">
+        <v>0</v>
+      </c>
+      <c r="BI2" s="11">
+        <v>0</v>
+      </c>
+      <c r="BK2" s="39" t="s">
+        <v>110</v>
+      </c>
+      <c r="BL2" s="42">
         <v>46025</v>
       </c>
-      <c r="BK2" s="8" t="s">
+      <c r="BM2" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="BN2" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="BL2" s="8" t="s">
+      <c r="BO2" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="BP2" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="BM2" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="BN2" s="11" t="s">
+      <c r="BQ2" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="BR2" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="BS2" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="BT2" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="BU2" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="BV2" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="BW2" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="BX2" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="BY2" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="BZ2" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="CA2" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="CB2" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="CC2" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="CD2" s="52" t="s">
         <v>268</v>
       </c>
-      <c r="BO2" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="BP2" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="BQ2" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="BR2" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="BS2" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="BT2" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="BU2" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="BV2" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="BW2" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="BX2" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="BY2" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="BZ2" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="CA2" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="CB2" s="52" t="s">
+      <c r="CE2" s="53">
+        <v>46145</v>
+      </c>
+      <c r="CF2" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="CC2" s="53">
-        <v>46145</v>
-      </c>
-      <c r="CD2" s="11" t="s">
-        <v>270</v>
-      </c>
-      <c r="CE2" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="CF2" s="11" t="s">
-        <v>282</v>
-      </c>
       <c r="CG2" s="11" t="s">
-        <v>299</v>
+        <v>266</v>
+      </c>
+      <c r="CH2" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="CI2" s="11" t="s">
+        <v>305</v>
       </c>
     </row>
-    <row r="3" spans="1:87" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:89" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
         <v>2</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C3" s="31">
         <v>46100</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F3" s="47" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>155</v>
+        <v>273</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="K3" s="11">
+        <v>154</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="L3" s="11">
         <v>76</v>
       </c>
-      <c r="L3" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="M3" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="N3" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="O3" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="P3" s="45" t="s">
-        <v>298</v>
-      </c>
-      <c r="Q3" s="38" t="s">
-        <v>302</v>
-      </c>
-      <c r="R3" s="15">
+      <c r="M3" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="N3" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="O3" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="P3" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q3" s="45" t="s">
+        <v>297</v>
+      </c>
+      <c r="R3" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="S3" s="15">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="S3" s="15">
+      <c r="T3" s="15">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="T3" s="15">
+      <c r="U3" s="15">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="U3" s="15">
+      <c r="V3" s="15">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="V3" s="7">
+      <c r="W3" s="7">
         <v>2951781</v>
       </c>
-      <c r="W3" s="34">
+      <c r="X3" s="34">
         <v>129878</v>
       </c>
-      <c r="X3" s="33">
+      <c r="Y3" s="33">
         <v>259756</v>
       </c>
-      <c r="Y3" s="38">
+      <c r="Z3" s="38">
         <v>15</v>
       </c>
-      <c r="Z3" s="32">
+      <c r="AA3" s="32">
         <v>9944</v>
       </c>
-      <c r="AA3" s="38">
+      <c r="AB3" s="38">
         <v>21</v>
       </c>
-      <c r="AB3" s="32">
+      <c r="AC3" s="32">
         <v>184914</v>
       </c>
-      <c r="AC3" s="38">
+      <c r="AD3" s="38">
         <v>3</v>
       </c>
-      <c r="AD3" s="32">
-        <v>0</v>
-      </c>
       <c r="AE3" s="32">
-        <v>454614</v>
+        <v>0</v>
       </c>
       <c r="AF3" s="32">
         <v>454614</v>
       </c>
       <c r="AG3" s="32">
+        <v>454614</v>
+      </c>
+      <c r="AH3" s="32"/>
+      <c r="AI3" s="32">
         <v>36465</v>
       </c>
-      <c r="AH3" s="32">
+      <c r="AJ3" s="32">
         <v>945693</v>
       </c>
-      <c r="AI3" s="32">
+      <c r="AK3" s="32">
         <v>945693</v>
       </c>
-      <c r="AJ3" s="23" t="s">
-        <v>287</v>
-      </c>
-      <c r="AK3" s="23" t="s">
-        <v>290</v>
-      </c>
-      <c r="AL3" s="27" t="s">
-        <v>294</v>
-      </c>
-      <c r="AM3" s="21"/>
-      <c r="AN3" s="22"/>
-      <c r="AO3" s="22"/>
+      <c r="AL3" s="23" t="s">
+        <v>286</v>
+      </c>
+      <c r="AM3" s="23" t="s">
+        <v>289</v>
+      </c>
+      <c r="AN3" s="27" t="s">
+        <v>293</v>
+      </c>
+      <c r="AO3" s="21"/>
       <c r="AP3" s="22"/>
-      <c r="AQ3" s="37" t="s">
-        <v>245</v>
-      </c>
-      <c r="AR3" s="37">
+      <c r="AQ3" s="22"/>
+      <c r="AR3" s="22"/>
+      <c r="AS3" s="37" t="s">
+        <v>244</v>
+      </c>
+      <c r="AT3" s="37">
         <v>36</v>
       </c>
-      <c r="AS3" t="s">
-        <v>257</v>
-      </c>
-      <c r="AT3" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="AU3" s="8" t="s">
-        <v>273</v>
+      <c r="AU3" t="s">
+        <v>256</v>
       </c>
       <c r="AV3" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="AW3" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="AW3" s="8">
+      <c r="AX3" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="AY3" s="8">
         <v>130000</v>
       </c>
-      <c r="AY3" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="AZ3" s="11">
-        <v>1</v>
-      </c>
-      <c r="BA3" s="11">
-        <v>1</v>
+      <c r="AZ3" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="BA3" s="8" t="s">
+        <v>274</v>
       </c>
       <c r="BB3" s="11">
         <v>1</v>
       </c>
       <c r="BC3" s="11">
+        <v>1</v>
+      </c>
+      <c r="BD3" s="11">
+        <v>1</v>
+      </c>
+      <c r="BE3" s="11">
         <v>2</v>
       </c>
-      <c r="BD3" s="11">
-        <v>0</v>
-      </c>
-      <c r="BE3" s="11">
-        <v>0</v>
-      </c>
       <c r="BF3" s="11">
+        <v>0</v>
+      </c>
+      <c r="BG3" s="11">
+        <v>0</v>
+      </c>
+      <c r="BH3" s="11">
         <v>1</v>
       </c>
-      <c r="BG3" s="11">
-        <v>0</v>
-      </c>
-      <c r="BI3" s="39" t="s">
-        <v>111</v>
-      </c>
-      <c r="BJ3" s="42">
+      <c r="BI3" s="11">
+        <v>0</v>
+      </c>
+      <c r="BK3" s="39" t="s">
+        <v>110</v>
+      </c>
+      <c r="BL3" s="42">
         <v>46025</v>
       </c>
-      <c r="BK3" s="8" t="s">
+      <c r="BM3" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="BN3" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="BL3" s="8" t="s">
+      <c r="BO3" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="BP3" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="BM3" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="BN3" s="11" t="s">
+      <c r="BQ3" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="BR3" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="BS3" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="BT3" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="BU3" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="BV3" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="BW3" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="BX3" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="BY3" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="BZ3" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="CA3" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="CB3" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="CC3" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="CD3" s="52" t="s">
         <v>268</v>
       </c>
-      <c r="BO3" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="BP3" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="BQ3" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="BR3" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="BS3" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="BT3" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="BU3" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="BV3" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="BW3" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="BX3" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="BY3" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="BZ3" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="CA3" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="CB3" s="52" t="s">
+      <c r="CE3" s="53">
+        <v>46145</v>
+      </c>
+      <c r="CF3" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="CC3" s="53">
-        <v>46145</v>
-      </c>
-      <c r="CD3" s="11" t="s">
-        <v>270</v>
-      </c>
-      <c r="CE3" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="CF3" s="11" t="s">
-        <v>282</v>
-      </c>
       <c r="CG3" s="11" t="s">
-        <v>299</v>
+        <v>266</v>
+      </c>
+      <c r="CH3" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="CI3" s="11" t="s">
+        <v>305</v>
       </c>
     </row>
-    <row r="4" spans="1:87" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:89" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C4" s="31">
         <v>46100</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F4" s="48" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>155</v>
+        <v>273</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="K4" s="11">
+        <v>154</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="L4" s="11">
         <v>76</v>
       </c>
-      <c r="L4" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="M4" s="12">
+      <c r="M4" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="N4" s="12">
         <v>1319</v>
       </c>
-      <c r="N4" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="O4" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="P4" s="14"/>
-      <c r="Q4" s="38" t="s">
-        <v>302</v>
-      </c>
-      <c r="R4" s="15">
+      <c r="O4" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="P4" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="S4" s="15">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="S4" s="15">
+      <c r="T4" s="15">
         <v>1.4E-2</v>
       </c>
-      <c r="T4" s="15">
+      <c r="U4" s="15">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="U4" s="15">
+      <c r="V4" s="15">
         <v>1.4E-2</v>
       </c>
-      <c r="V4" s="7">
+      <c r="W4" s="7">
         <v>2951781</v>
       </c>
-      <c r="W4" s="34">
+      <c r="X4" s="34">
         <v>103312</v>
       </c>
-      <c r="X4" s="33">
+      <c r="Y4" s="33">
         <v>206624</v>
       </c>
-      <c r="Y4" s="38">
+      <c r="Z4" s="38">
         <v>17</v>
       </c>
-      <c r="Z4" s="32">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="35"/>
-      <c r="AB4" s="32">
+      <c r="AA4" s="32">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="35"/>
+      <c r="AC4" s="32">
         <v>380187</v>
       </c>
-      <c r="AC4" s="35">
+      <c r="AD4" s="35">
         <v>8</v>
       </c>
-      <c r="AD4" s="32">
+      <c r="AE4" s="32">
         <v>422890</v>
-      </c>
-      <c r="AE4" s="32">
-        <v>1009701</v>
       </c>
       <c r="AF4" s="32">
         <v>1009701</v>
       </c>
       <c r="AG4" s="32">
+        <v>1009701</v>
+      </c>
+      <c r="AH4" s="32"/>
+      <c r="AI4" s="32">
         <v>29007</v>
       </c>
-      <c r="AH4" s="32">
+      <c r="AJ4" s="32">
         <v>2048409</v>
       </c>
-      <c r="AI4" s="17"/>
-      <c r="AL4" s="27" t="s">
-        <v>293</v>
-      </c>
-      <c r="AM4" s="24" t="s">
+      <c r="AK4" s="17"/>
+      <c r="AN4" s="27" t="s">
+        <v>292</v>
+      </c>
+      <c r="AO4" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="AP4" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="AN4" s="8" t="s">
+      <c r="AQ4" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="AO4" s="8" t="s">
+      <c r="AR4" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="AP4" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="AQ4" s="37" t="s">
-        <v>245</v>
-      </c>
-      <c r="AS4" t="s">
-        <v>257</v>
-      </c>
-      <c r="AT4" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="AU4" s="8" t="s">
-        <v>273</v>
+      <c r="AS4" s="37" t="s">
+        <v>244</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>256</v>
       </c>
       <c r="AV4" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="AW4" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="AW4" s="8">
+      <c r="AX4" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="AY4" s="8">
         <v>130000</v>
       </c>
-      <c r="AY4" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="AZ4" s="11">
-        <v>1</v>
-      </c>
-      <c r="BA4" s="11">
-        <v>1</v>
+      <c r="BA4" s="8" t="s">
+        <v>274</v>
       </c>
       <c r="BB4" s="11">
         <v>1</v>
       </c>
       <c r="BC4" s="11">
+        <v>1</v>
+      </c>
+      <c r="BD4" s="11">
+        <v>1</v>
+      </c>
+      <c r="BE4" s="11">
         <v>2</v>
       </c>
-      <c r="BD4" s="11">
-        <v>0</v>
-      </c>
-      <c r="BE4" s="11">
-        <v>0</v>
-      </c>
       <c r="BF4" s="11">
+        <v>0</v>
+      </c>
+      <c r="BG4" s="11">
+        <v>0</v>
+      </c>
+      <c r="BH4" s="11">
         <v>1</v>
       </c>
-      <c r="BG4" s="11">
-        <v>0</v>
-      </c>
-      <c r="BI4" s="39" t="s">
-        <v>111</v>
-      </c>
-      <c r="BJ4" s="42">
+      <c r="BI4" s="11">
+        <v>0</v>
+      </c>
+      <c r="BK4" s="39" t="s">
+        <v>110</v>
+      </c>
+      <c r="BL4" s="42">
         <v>46025</v>
       </c>
-      <c r="BK4" s="8" t="s">
+      <c r="BM4" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="BN4" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="BL4" s="8" t="s">
+      <c r="BO4" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="BP4" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="BM4" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="BN4" s="11" t="s">
+      <c r="BQ4" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="BR4" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="BS4" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="BT4" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="BU4" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="BV4" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="BW4" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="BX4" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="BY4" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="BZ4" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="CA4" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="CB4" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="CC4" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="CD4" s="52" t="s">
         <v>268</v>
       </c>
-      <c r="BO4" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="BP4" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="BQ4" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="BR4" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="BS4" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="BT4" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="BU4" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="BV4" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="BW4" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="BX4" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="BY4" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="BZ4" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="CA4" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="CB4" s="52" t="s">
+      <c r="CE4" s="53">
+        <v>46145</v>
+      </c>
+      <c r="CF4" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="CC4" s="53">
-        <v>46145</v>
-      </c>
-      <c r="CD4" s="11" t="s">
-        <v>270</v>
-      </c>
-      <c r="CE4" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="CF4" s="11" t="s">
-        <v>282</v>
-      </c>
       <c r="CG4" s="11" t="s">
-        <v>299</v>
+        <v>266</v>
+      </c>
+      <c r="CH4" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="CI4" s="11" t="s">
+        <v>305</v>
       </c>
     </row>
-    <row r="5" spans="1:87" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:89" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C5" s="31">
         <v>46100</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>155</v>
+        <v>158</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="K5" s="11">
+        <v>154</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="L5" s="11">
         <v>76</v>
       </c>
-      <c r="L5" s="11">
+      <c r="M5" s="11">
         <v>172</v>
       </c>
-      <c r="M5" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="N5" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="O5" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="P5" s="45" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q5" s="38" t="s">
-        <v>302</v>
-      </c>
-      <c r="R5" s="55">
+      <c r="N5" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="O5" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="P5" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q5" s="45" t="s">
+        <v>296</v>
+      </c>
+      <c r="R5" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="S5" s="55">
         <v>0.2409</v>
       </c>
-      <c r="S5" s="56">
+      <c r="T5" s="56">
         <v>9.7500000000000003E-2</v>
       </c>
-      <c r="T5" s="15">
+      <c r="U5" s="15">
         <v>0.2409</v>
       </c>
-      <c r="U5" s="15">
+      <c r="V5" s="15">
         <v>9.7500000000000003E-2</v>
       </c>
-      <c r="V5" s="32">
+      <c r="W5" s="32">
         <v>2498838</v>
       </c>
-      <c r="W5" s="34">
+      <c r="X5" s="34">
         <v>601970</v>
       </c>
-      <c r="X5" s="33">
+      <c r="Y5" s="33">
         <v>1203940</v>
       </c>
-      <c r="Z5" s="32">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="35"/>
-      <c r="AB5" s="32">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="35"/>
-      <c r="AD5" s="32">
-        <v>0</v>
-      </c>
+      <c r="AA5" s="32">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="35"/>
+      <c r="AC5" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="35"/>
       <c r="AE5" s="32">
-        <v>1203940</v>
+        <v>0</v>
       </c>
       <c r="AF5" s="32">
         <v>1203940</v>
       </c>
       <c r="AG5" s="32">
+        <v>1203940</v>
+      </c>
+      <c r="AH5" s="32"/>
+      <c r="AI5" s="32">
         <v>169013</v>
       </c>
-      <c r="AH5" s="32">
+      <c r="AJ5" s="32">
         <v>2576893</v>
       </c>
-      <c r="AI5" s="50">
+      <c r="AK5" s="50">
         <v>50000</v>
       </c>
-      <c r="AJ5" s="49" t="s">
-        <v>288</v>
-      </c>
-      <c r="AK5" s="11" t="s">
-        <v>291</v>
-      </c>
-      <c r="AL5" s="27"/>
-      <c r="AM5" s="24" t="s">
-        <v>182</v>
-      </c>
-      <c r="AN5" s="8" t="s">
+      <c r="AL5" s="49" t="s">
+        <v>287</v>
+      </c>
+      <c r="AM5" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="AN5" s="27"/>
+      <c r="AO5" s="24" t="s">
+        <v>181</v>
+      </c>
+      <c r="AP5" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="AQ5" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="AO5" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="AP5" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="AQ5" s="37" t="s">
-        <v>246</v>
-      </c>
-      <c r="AR5" s="37">
+      <c r="AR5" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="AS5" s="37" t="s">
+        <v>245</v>
+      </c>
+      <c r="AT5" s="37">
         <v>78</v>
       </c>
-      <c r="AS5" s="37" t="s">
+      <c r="AU5" s="37" t="s">
+        <v>247</v>
+      </c>
+      <c r="AV5" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="AT5" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="AZ5" s="11">
+      <c r="BB5" s="11">
         <v>1</v>
-      </c>
-      <c r="BA5" s="11">
-        <v>1</v>
-      </c>
-      <c r="BB5" s="11">
-        <v>2</v>
       </c>
       <c r="BC5" s="11">
         <v>1</v>
       </c>
       <c r="BD5" s="11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BE5" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF5" s="11">
         <v>0</v>
       </c>
       <c r="BG5" s="11">
+        <v>0</v>
+      </c>
+      <c r="BH5" s="11">
+        <v>0</v>
+      </c>
+      <c r="BI5" s="11">
         <v>2</v>
       </c>
-      <c r="BH5" s="54" t="s">
-        <v>253</v>
-      </c>
-      <c r="BI5" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="BJ5" s="43">
+      <c r="BJ5" s="54" t="s">
+        <v>252</v>
+      </c>
+      <c r="BK5" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="BL5" s="43">
         <v>46037</v>
       </c>
-      <c r="BK5" s="8" t="s">
+      <c r="BM5" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="BN5" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="BL5" s="8" t="s">
+      <c r="BO5" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="BM5" s="8" t="s">
+      <c r="BP5" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="BQ5" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="BR5" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="BS5" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="BT5" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="BU5" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="BV5" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="BW5" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="BX5" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="BY5" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="BZ5" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="CA5" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="CB5" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="CC5" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="CD5" s="52" t="s">
+        <v>268</v>
+      </c>
+      <c r="CE5" s="53">
+        <v>46145</v>
+      </c>
+      <c r="CF5" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="CG5" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="CH5" s="11" t="s">
         <v>280</v>
       </c>
-      <c r="BN5" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="BO5" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="BP5" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="BQ5" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="BR5" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="BS5" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="BT5" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="BU5" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="BV5" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="BW5" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="BX5" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="BY5" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="BZ5" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="CA5" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="CB5" s="52" t="s">
-        <v>269</v>
-      </c>
-      <c r="CC5" s="53">
-        <v>46145</v>
-      </c>
-      <c r="CD5" s="11" t="s">
-        <v>278</v>
-      </c>
-      <c r="CE5" s="11" t="s">
-        <v>279</v>
-      </c>
-      <c r="CF5" s="11" t="s">
-        <v>281</v>
-      </c>
-      <c r="CG5" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="CH5" s="53">
+      <c r="CI5" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="CJ5" s="53">
         <v>46102</v>
       </c>
-      <c r="CI5" s="11">
+      <c r="CK5" s="11">
         <v>20000</v>
       </c>
     </row>
-    <row r="6" spans="1:87" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:89" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <v>5</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C6" s="31">
         <v>46100</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F6" s="46" t="s">
-        <v>255</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>155</v>
+        <v>254</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="K6" s="11">
+        <v>154</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="L6" s="11">
         <v>76</v>
       </c>
-      <c r="L6" s="11">
+      <c r="M6" s="11">
         <v>172</v>
       </c>
-      <c r="M6" s="12"/>
-      <c r="N6" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="O6" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="P6" s="14"/>
-      <c r="Q6" s="38" t="s">
-        <v>302</v>
-      </c>
-      <c r="R6" s="56">
+      <c r="N6" s="12"/>
+      <c r="O6" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="P6" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q6" s="14"/>
+      <c r="R6" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="S6" s="56">
         <v>0.2409</v>
       </c>
-      <c r="S6" s="56">
+      <c r="T6" s="56">
         <v>9.7500000000000003E-2</v>
       </c>
-      <c r="T6" s="30">
+      <c r="U6" s="30">
         <v>0.2409</v>
       </c>
-      <c r="U6" s="15">
+      <c r="V6" s="15">
         <v>9.7500000000000003E-2</v>
       </c>
-      <c r="V6" s="32">
+      <c r="W6" s="32">
         <v>2498838</v>
       </c>
-      <c r="W6" s="34">
+      <c r="X6" s="34">
         <v>601970</v>
       </c>
-      <c r="X6" s="33">
+      <c r="Y6" s="33">
         <v>1203940</v>
       </c>
-      <c r="Z6" s="32"/>
-      <c r="AA6" s="35"/>
-      <c r="AB6" s="32"/>
-      <c r="AC6" s="35"/>
-      <c r="AD6" s="32"/>
+      <c r="AA6" s="32"/>
+      <c r="AB6" s="35"/>
+      <c r="AC6" s="32"/>
+      <c r="AD6" s="35"/>
       <c r="AE6" s="32"/>
       <c r="AF6" s="32"/>
       <c r="AG6" s="32"/>
       <c r="AH6" s="32"/>
-      <c r="AI6" s="50">
+      <c r="AI6" s="32"/>
+      <c r="AJ6" s="32"/>
+      <c r="AK6" s="50">
         <v>40000</v>
       </c>
-      <c r="AM6" s="24" t="s">
-        <v>183</v>
-      </c>
-      <c r="AN6" s="8" t="s">
+      <c r="AO6" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="AP6" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="AQ6" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="AO6" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="AP6" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="AQ6" s="37" t="s">
+      <c r="AR6" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="AS6" s="37" t="s">
+        <v>246</v>
+      </c>
+      <c r="AT6" s="37">
+        <v>73</v>
+      </c>
+      <c r="AU6" s="37" t="s">
         <v>247</v>
       </c>
-      <c r="AR6" s="37">
-        <v>73</v>
-      </c>
-      <c r="AS6" s="37" t="s">
+      <c r="AV6" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="AT6" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="AZ6" s="11">
+      <c r="BB6" s="11">
         <v>1</v>
-      </c>
-      <c r="BA6" s="11">
-        <v>1</v>
-      </c>
-      <c r="BB6" s="11">
-        <v>2</v>
       </c>
       <c r="BC6" s="11">
         <v>1</v>
       </c>
       <c r="BD6" s="11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BE6" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF6" s="11">
         <v>0</v>
       </c>
       <c r="BG6" s="11">
+        <v>0</v>
+      </c>
+      <c r="BH6" s="11">
+        <v>0</v>
+      </c>
+      <c r="BI6" s="11">
         <v>1</v>
       </c>
-      <c r="BH6" s="54" t="s">
-        <v>253</v>
-      </c>
-      <c r="BI6" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="BJ6" s="43">
+      <c r="BJ6" s="54" t="s">
+        <v>252</v>
+      </c>
+      <c r="BK6" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="BL6" s="43">
         <v>46037</v>
       </c>
-      <c r="BK6" s="8" t="s">
+      <c r="BM6" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="BN6" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="BL6" s="8" t="s">
+      <c r="BO6" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="BM6" s="8" t="s">
+      <c r="BP6" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="BQ6" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="BR6" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="BS6" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="BT6" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="BU6" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="BV6" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="BW6" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="BX6" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="BY6" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="BZ6" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="CA6" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="CB6" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="CC6" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="CD6" s="52" t="s">
+        <v>268</v>
+      </c>
+      <c r="CE6" s="53">
+        <v>46145</v>
+      </c>
+      <c r="CF6" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="CG6" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="CH6" s="11" t="s">
         <v>280</v>
       </c>
-      <c r="BN6" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="BO6" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="BP6" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="BQ6" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="BR6" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="BS6" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="BT6" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="BU6" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="BV6" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="BW6" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="BX6" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="BY6" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="BZ6" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="CA6" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="CB6" s="52" t="s">
-        <v>269</v>
-      </c>
-      <c r="CC6" s="53">
-        <v>46145</v>
-      </c>
-      <c r="CD6" s="11" t="s">
-        <v>278</v>
-      </c>
-      <c r="CE6" s="11" t="s">
-        <v>279</v>
-      </c>
-      <c r="CF6" s="11" t="s">
-        <v>281</v>
-      </c>
-      <c r="CG6" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="CH6" s="53">
+      <c r="CI6" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="CJ6" s="53">
         <v>46102</v>
       </c>
-      <c r="CI6" s="11">
+      <c r="CK6" s="11">
         <v>20000</v>
       </c>
     </row>
-    <row r="7" spans="1:87" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:89" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
         <v>6</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C7" s="31">
         <v>46100</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F7" s="46" t="s">
-        <v>254</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>155</v>
+        <v>253</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="K7" s="11">
+        <v>154</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="L7" s="11">
         <v>76</v>
       </c>
-      <c r="L7" s="11">
+      <c r="M7" s="11">
         <v>172</v>
       </c>
-      <c r="M7" s="12"/>
-      <c r="N7" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="O7" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="P7" s="14"/>
-      <c r="Q7" s="38" t="s">
-        <v>302</v>
-      </c>
-      <c r="R7" s="56">
+      <c r="N7" s="12"/>
+      <c r="O7" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="P7" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q7" s="14"/>
+      <c r="R7" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="S7" s="56">
         <v>0.2409</v>
       </c>
-      <c r="S7" s="56">
+      <c r="T7" s="56">
         <v>9.7500000000000003E-2</v>
       </c>
-      <c r="T7" s="30">
+      <c r="U7" s="30">
         <v>0.2409</v>
       </c>
-      <c r="U7" s="15">
+      <c r="V7" s="15">
         <v>9.7500000000000003E-2</v>
       </c>
-      <c r="V7" s="32">
+      <c r="W7" s="32">
         <v>2498838</v>
       </c>
-      <c r="W7" s="34">
+      <c r="X7" s="34">
         <v>601970</v>
       </c>
-      <c r="X7" s="33">
+      <c r="Y7" s="33">
         <v>1203940</v>
       </c>
-      <c r="Z7" s="32"/>
-      <c r="AA7" s="35"/>
-      <c r="AB7" s="32"/>
-      <c r="AC7" s="35"/>
-      <c r="AD7" s="32"/>
+      <c r="AA7" s="32"/>
+      <c r="AB7" s="35"/>
+      <c r="AC7" s="32"/>
+      <c r="AD7" s="35"/>
       <c r="AE7" s="32"/>
       <c r="AF7" s="32"/>
       <c r="AG7" s="32"/>
       <c r="AH7" s="32"/>
-      <c r="AI7" s="50">
+      <c r="AI7" s="32"/>
+      <c r="AJ7" s="32"/>
+      <c r="AK7" s="50">
         <v>20000</v>
       </c>
-      <c r="AM7" s="24" t="s">
-        <v>184</v>
-      </c>
-      <c r="AN7" s="8" t="s">
+      <c r="AO7" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="AP7" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="AQ7" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="AO7" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="AP7" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="AQ7" s="37" t="s">
-        <v>256</v>
-      </c>
-      <c r="AR7" s="37">
+      <c r="AR7" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="AS7" s="37" t="s">
+        <v>255</v>
+      </c>
+      <c r="AT7" s="37">
         <v>55</v>
       </c>
-      <c r="AS7" s="37" t="s">
+      <c r="AU7" s="37" t="s">
+        <v>247</v>
+      </c>
+      <c r="AV7" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="AT7" s="8" t="s">
+      <c r="AW7" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="AX7" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="AU7" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="AV7" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="AY7" s="27" t="s">
-        <v>283</v>
-      </c>
-      <c r="AZ7" s="11">
+      <c r="BA7" s="27" t="s">
+        <v>282</v>
+      </c>
+      <c r="BB7" s="11">
         <v>2</v>
-      </c>
-      <c r="BA7" s="11">
-        <v>1</v>
-      </c>
-      <c r="BB7" s="11">
-        <v>1</v>
       </c>
       <c r="BC7" s="11">
         <v>1</v>
       </c>
       <c r="BD7" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE7" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF7" s="11">
         <v>0</v>
@@ -3237,391 +3279,403 @@
       <c r="BG7" s="11">
         <v>0</v>
       </c>
-      <c r="BH7" s="54" t="s">
-        <v>253</v>
-      </c>
-      <c r="BI7" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="BJ7" s="43">
+      <c r="BH7" s="11">
+        <v>0</v>
+      </c>
+      <c r="BI7" s="11">
+        <v>0</v>
+      </c>
+      <c r="BJ7" s="54" t="s">
+        <v>252</v>
+      </c>
+      <c r="BK7" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="BL7" s="43">
         <v>46037</v>
       </c>
-      <c r="BK7" s="8" t="s">
+      <c r="BM7" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="BN7" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="BL7" s="8" t="s">
+      <c r="BO7" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="BM7" s="8" t="s">
+      <c r="BP7" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="BQ7" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="BR7" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="BS7" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="BT7" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="BU7" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="BV7" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="BW7" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="BX7" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="BY7" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="BZ7" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="CA7" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="CB7" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="CC7" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="CD7" s="52" t="s">
+        <v>268</v>
+      </c>
+      <c r="CE7" s="53">
+        <v>46145</v>
+      </c>
+      <c r="CF7" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="CG7" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="CH7" s="11" t="s">
         <v>280</v>
       </c>
-      <c r="BN7" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="BO7" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="BP7" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="BQ7" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="BR7" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="BS7" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="BT7" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="BU7" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="BV7" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="BW7" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="BX7" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="BY7" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="BZ7" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="CA7" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="CB7" s="52" t="s">
-        <v>269</v>
-      </c>
-      <c r="CC7" s="53">
-        <v>46145</v>
-      </c>
-      <c r="CD7" s="11" t="s">
-        <v>270</v>
-      </c>
-      <c r="CE7" s="11" t="s">
-        <v>279</v>
-      </c>
-      <c r="CF7" s="11" t="s">
-        <v>281</v>
-      </c>
-      <c r="CG7" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="CH7" s="53">
+      <c r="CI7" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="CJ7" s="53">
         <v>46102</v>
       </c>
-      <c r="CI7" s="11">
+      <c r="CK7" s="11">
         <v>20000</v>
       </c>
     </row>
-    <row r="8" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:89" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>7</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C8" s="31">
         <v>46100</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>155</v>
+        <v>99</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="K8" s="11">
+        <v>154</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="L8" s="11">
         <v>76</v>
       </c>
-      <c r="L8" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="M8" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="N8" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="O8" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="P8" s="14"/>
-      <c r="Q8" s="38" t="s">
-        <v>302</v>
-      </c>
-      <c r="R8" s="15">
+      <c r="M8" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="N8" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="O8" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="P8" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="S8" s="15">
         <v>9.0200000000000002E-2</v>
       </c>
-      <c r="S8" s="15">
+      <c r="T8" s="15">
         <v>3.6499999999999998E-2</v>
       </c>
-      <c r="T8" s="15">
+      <c r="U8" s="15">
         <v>9.0200000000000002E-2</v>
       </c>
-      <c r="U8" s="15">
+      <c r="V8" s="15">
         <v>3.6499999999999998E-2</v>
       </c>
-      <c r="V8" s="32">
+      <c r="W8" s="32">
         <v>2498838</v>
       </c>
-      <c r="W8" s="34">
+      <c r="X8" s="34">
         <v>225395</v>
       </c>
-      <c r="X8" s="33">
+      <c r="Y8" s="33">
         <v>450790</v>
       </c>
-      <c r="Z8" s="32">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="35"/>
-      <c r="AB8" s="32">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="35"/>
-      <c r="AD8" s="32">
-        <v>0</v>
-      </c>
+      <c r="AA8" s="32">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="35"/>
+      <c r="AC8" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="35"/>
       <c r="AE8" s="32">
-        <v>450790</v>
+        <v>0</v>
       </c>
       <c r="AF8" s="32">
         <v>450790</v>
       </c>
       <c r="AG8" s="32">
+        <v>450790</v>
+      </c>
+      <c r="AH8" s="32"/>
+      <c r="AI8" s="32">
         <v>63284</v>
       </c>
-      <c r="AH8" s="32">
+      <c r="AJ8" s="32">
         <v>964864</v>
       </c>
-      <c r="AI8" s="17"/>
-      <c r="AM8" s="24" t="s">
+      <c r="AK8" s="17"/>
+      <c r="AO8" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="AP8" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="AN8" s="8" t="s">
+      <c r="AQ8" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="AO8" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="AP8" s="8" t="s">
-        <v>190</v>
+      <c r="AR8" s="8" t="s">
+        <v>189</v>
       </c>
     </row>
-    <row r="9" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:89" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C9" s="31">
         <v>46100</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>101</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>155</v>
+        <v>100</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="K9" s="11">
+        <v>154</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="L9" s="11">
         <v>76</v>
       </c>
-      <c r="L9" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="M9" s="11" t="s">
-        <v>131</v>
+      <c r="M9" s="9" t="s">
+        <v>90</v>
       </c>
       <c r="N9" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="O9" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="P9" s="14"/>
-      <c r="Q9" s="38" t="s">
-        <v>303</v>
-      </c>
-      <c r="R9" s="6"/>
-      <c r="S9" s="14"/>
-      <c r="T9" s="15">
+        <v>130</v>
+      </c>
+      <c r="O9" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="P9" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q9" s="14"/>
+      <c r="R9" s="38" t="s">
+        <v>300</v>
+      </c>
+      <c r="S9" s="6"/>
+      <c r="T9" s="14"/>
+      <c r="U9" s="15">
         <v>0.19400000000000001</v>
       </c>
-      <c r="U9" s="15">
+      <c r="V9" s="15">
         <v>7.85E-2</v>
       </c>
-      <c r="V9" s="32">
+      <c r="W9" s="32">
         <v>2536416</v>
       </c>
-      <c r="W9" s="34">
+      <c r="X9" s="34">
         <v>492065</v>
       </c>
-      <c r="X9" s="33">
+      <c r="Y9" s="33">
         <v>984130</v>
       </c>
-      <c r="Z9" s="32">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="35"/>
-      <c r="AB9" s="32">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="35"/>
-      <c r="AD9" s="32">
-        <v>0</v>
-      </c>
+      <c r="AA9" s="32">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="35"/>
+      <c r="AC9" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="35"/>
       <c r="AE9" s="32">
-        <v>984130</v>
+        <v>0</v>
       </c>
       <c r="AF9" s="32">
         <v>984130</v>
       </c>
       <c r="AG9" s="32">
+        <v>984130</v>
+      </c>
+      <c r="AH9" s="32"/>
+      <c r="AI9" s="32">
         <v>138156</v>
       </c>
-      <c r="AH9" s="32">
+      <c r="AJ9" s="32">
         <v>2106416</v>
       </c>
-      <c r="AI9" s="17"/>
-      <c r="AM9" s="18" t="s">
+      <c r="AK9" s="17"/>
+      <c r="AO9" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="AP9" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="AQ9" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="AR9" s="19" t="s">
         <v>194</v>
       </c>
-      <c r="AN9" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="AO9" s="19" t="s">
-        <v>180</v>
-      </c>
-      <c r="AP9" s="19" t="s">
-        <v>195</v>
-      </c>
     </row>
-    <row r="10" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:89" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <v>9</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C10" s="31">
         <v>46100</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>101</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>155</v>
+        <v>100</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="K10" s="11">
+        <v>154</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="L10" s="11">
         <v>76</v>
       </c>
-      <c r="L10" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="M10" s="11" t="s">
-        <v>132</v>
+      <c r="M10" s="9" t="s">
+        <v>90</v>
       </c>
       <c r="N10" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="O10" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q10" s="38" t="s">
-        <v>302</v>
-      </c>
-      <c r="R10" s="15">
+        <v>131</v>
+      </c>
+      <c r="O10" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="P10" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="R10" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="S10" s="15">
         <v>0.1426</v>
       </c>
-      <c r="S10" s="15">
+      <c r="T10" s="15">
         <v>5.7700000000000001E-2</v>
       </c>
-      <c r="T10" s="15">
+      <c r="U10" s="15">
         <v>0.1426</v>
       </c>
-      <c r="U10" s="15">
+      <c r="V10" s="15">
         <v>5.7700000000000001E-2</v>
       </c>
-      <c r="V10" s="32">
+      <c r="W10" s="32">
         <v>2536416</v>
       </c>
-      <c r="W10" s="34">
+      <c r="X10" s="34">
         <v>361693</v>
       </c>
-      <c r="X10" s="33">
+      <c r="Y10" s="33">
         <v>723386</v>
       </c>
-      <c r="Z10" s="32">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="35"/>
-      <c r="AB10" s="32">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="35"/>
-      <c r="AD10" s="32">
-        <v>0</v>
-      </c>
+      <c r="AA10" s="32">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="35"/>
+      <c r="AC10" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="35"/>
       <c r="AE10" s="32">
-        <v>723386</v>
+        <v>0</v>
       </c>
       <c r="AF10" s="32">
         <v>723386</v>
       </c>
       <c r="AG10" s="32">
+        <v>723386</v>
+      </c>
+      <c r="AH10" s="32"/>
+      <c r="AI10" s="32">
         <v>101552</v>
       </c>
-      <c r="AH10" s="32">
+      <c r="AJ10" s="32">
         <v>1548324</v>
       </c>
-      <c r="AI10" s="17"/>
-      <c r="AM10" s="21"/>
-      <c r="AN10" s="22"/>
-      <c r="AO10" s="22"/>
+      <c r="AK10" s="17"/>
+      <c r="AO10" s="21"/>
       <c r="AP10" s="22"/>
-      <c r="BA10" s="11">
+      <c r="AQ10" s="22"/>
+      <c r="AR10" s="22"/>
+      <c r="BC10" s="11">
         <v>2</v>
-      </c>
-      <c r="BB10" s="11">
-        <v>3</v>
-      </c>
-      <c r="BC10" s="11">
-        <v>4</v>
       </c>
       <c r="BD10" s="11">
         <v>3</v>
@@ -3630,2311 +3684,2403 @@
         <v>4</v>
       </c>
       <c r="BF10" s="11">
+        <v>3</v>
+      </c>
+      <c r="BG10" s="11">
+        <v>4</v>
+      </c>
+      <c r="BH10" s="11">
         <v>1</v>
       </c>
-      <c r="BG10" s="11">
+      <c r="BI10" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:89" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
         <v>10</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C11" s="31">
         <v>46100</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>155</v>
+        <v>101</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="K11" s="11">
+        <v>154</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="L11" s="11">
         <v>76</v>
       </c>
-      <c r="L11" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="M11" s="11" t="s">
-        <v>133</v>
+      <c r="M11" s="9" t="s">
+        <v>91</v>
       </c>
       <c r="N11" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="O11" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q11" s="38" t="s">
-        <v>302</v>
-      </c>
-      <c r="R11" s="15">
+        <v>132</v>
+      </c>
+      <c r="O11" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="P11" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="R11" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="S11" s="15">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="S11" s="15">
+      <c r="T11" s="15">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="T11" s="15">
+      <c r="U11" s="15">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="U11" s="15">
+      <c r="V11" s="15">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="V11" s="32">
+      <c r="W11" s="32">
         <v>2303422</v>
       </c>
-      <c r="W11" s="34">
+      <c r="X11" s="34">
         <v>85227</v>
       </c>
-      <c r="X11" s="33">
+      <c r="Y11" s="33">
         <v>170454</v>
       </c>
-      <c r="Z11" s="32">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="35"/>
-      <c r="AB11" s="32">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="35"/>
-      <c r="AD11" s="32">
-        <v>0</v>
-      </c>
+      <c r="AA11" s="32">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="35"/>
+      <c r="AC11" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="35"/>
       <c r="AE11" s="32">
-        <v>170454</v>
+        <v>0</v>
       </c>
       <c r="AF11" s="32">
         <v>170454</v>
       </c>
       <c r="AG11" s="32">
+        <v>170454</v>
+      </c>
+      <c r="AH11" s="32"/>
+      <c r="AI11" s="32">
         <v>23929</v>
       </c>
-      <c r="AH11" s="32">
+      <c r="AJ11" s="32">
         <v>364837</v>
       </c>
-      <c r="AI11" s="17"/>
-      <c r="AM11" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="AN11" s="19" t="s">
+      <c r="AK11" s="17"/>
+      <c r="AO11" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="AP11" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="AQ11" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="AO11" s="19" t="s">
-        <v>180</v>
-      </c>
-      <c r="AP11" s="19" t="s">
-        <v>196</v>
+      <c r="AR11" s="19" t="s">
+        <v>195</v>
       </c>
     </row>
-    <row r="12" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:89" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
         <v>11</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C12" s="31">
         <v>46100</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>155</v>
+        <v>101</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="K12" s="11">
+        <v>154</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="L12" s="11">
         <v>76</v>
       </c>
-      <c r="L12" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="M12" s="11" t="s">
-        <v>134</v>
+      <c r="M12" s="9" t="s">
+        <v>91</v>
       </c>
       <c r="N12" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="O12" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q12" s="38" t="s">
-        <v>302</v>
-      </c>
-      <c r="R12" s="15">
+        <v>133</v>
+      </c>
+      <c r="O12" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="P12" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="R12" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="S12" s="15">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="S12" s="15">
+      <c r="T12" s="15">
         <v>2.2499999999999999E-2</v>
       </c>
-      <c r="T12" s="15">
+      <c r="U12" s="15">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="U12" s="15">
+      <c r="V12" s="15">
         <v>2.2499999999999999E-2</v>
       </c>
-      <c r="V12" s="32">
+      <c r="W12" s="32">
         <v>2303422</v>
       </c>
-      <c r="W12" s="34">
+      <c r="X12" s="34">
         <v>128992</v>
       </c>
-      <c r="X12" s="33">
+      <c r="Y12" s="33">
         <v>257984</v>
       </c>
-      <c r="Y12" s="8">
+      <c r="Z12" s="8">
         <v>7</v>
       </c>
-      <c r="Z12" s="32">
+      <c r="AA12" s="32">
         <v>34198</v>
       </c>
-      <c r="AA12" s="35">
+      <c r="AB12" s="35">
         <v>19</v>
       </c>
-      <c r="AB12" s="32">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="35">
+      <c r="AC12" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="35">
         <v>24</v>
       </c>
-      <c r="AD12" s="32">
-        <v>0</v>
-      </c>
       <c r="AE12" s="32">
-        <v>292182</v>
+        <v>0</v>
       </c>
       <c r="AF12" s="32">
         <v>292182</v>
       </c>
       <c r="AG12" s="32">
+        <v>292182</v>
+      </c>
+      <c r="AH12" s="32"/>
+      <c r="AI12" s="32">
         <v>36217</v>
       </c>
-      <c r="AH12" s="32">
+      <c r="AJ12" s="32">
         <v>620581</v>
       </c>
-      <c r="AI12" s="17"/>
-      <c r="AM12" s="26"/>
-      <c r="AN12" s="25"/>
-      <c r="AO12" s="25"/>
+      <c r="AK12" s="17"/>
+      <c r="AO12" s="26"/>
       <c r="AP12" s="25"/>
+      <c r="AQ12" s="25"/>
+      <c r="AR12" s="25"/>
     </row>
-    <row r="13" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:89" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
         <v>12</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C13" s="31">
         <v>46100</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>155</v>
+        <v>101</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="K13" s="11">
+        <v>154</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="L13" s="11">
         <v>76</v>
       </c>
-      <c r="L13" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="M13" s="11" t="s">
-        <v>135</v>
+      <c r="M13" s="9" t="s">
+        <v>91</v>
       </c>
       <c r="N13" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="O13" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q13" s="38" t="s">
-        <v>302</v>
-      </c>
-      <c r="R13" s="15">
+        <v>134</v>
+      </c>
+      <c r="O13" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="P13" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="R13" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="S13" s="15">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="S13" s="15">
+      <c r="T13" s="15">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="T13" s="15">
+      <c r="U13" s="15">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="U13" s="15">
+      <c r="V13" s="15">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="V13" s="32">
+      <c r="W13" s="32">
         <v>2303422</v>
       </c>
-      <c r="W13" s="34">
+      <c r="X13" s="34">
         <v>85227</v>
       </c>
-      <c r="X13" s="33">
+      <c r="Y13" s="33">
         <v>170454</v>
       </c>
-      <c r="Z13" s="32">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="35"/>
-      <c r="AB13" s="32">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="35"/>
-      <c r="AD13" s="32">
-        <v>0</v>
-      </c>
+      <c r="AA13" s="32">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="35"/>
+      <c r="AC13" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="35"/>
       <c r="AE13" s="32">
-        <v>170454</v>
+        <v>0</v>
       </c>
       <c r="AF13" s="32">
         <v>170454</v>
       </c>
       <c r="AG13" s="32">
+        <v>170454</v>
+      </c>
+      <c r="AH13" s="32"/>
+      <c r="AI13" s="32">
         <v>23929</v>
       </c>
-      <c r="AH13" s="32">
+      <c r="AJ13" s="32">
         <v>364837</v>
       </c>
-      <c r="AI13" s="17"/>
-      <c r="AM13" s="21"/>
-      <c r="AN13" s="22"/>
-      <c r="AO13" s="22"/>
+      <c r="AK13" s="17"/>
+      <c r="AO13" s="21"/>
       <c r="AP13" s="22"/>
-      <c r="BG13" s="8">
+      <c r="AQ13" s="22"/>
+      <c r="AR13" s="22"/>
+      <c r="BI13" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:89" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
         <v>13</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C14" s="31">
         <v>46100</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>155</v>
+        <v>102</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="K14" s="11">
+        <v>154</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="L14" s="11">
         <v>76</v>
       </c>
-      <c r="L14" s="11" t="s">
-        <v>93</v>
-      </c>
       <c r="M14" s="11" t="s">
-        <v>136</v>
+        <v>92</v>
       </c>
       <c r="N14" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="O14" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q14" s="38" t="s">
-        <v>302</v>
-      </c>
-      <c r="R14" s="15">
+        <v>135</v>
+      </c>
+      <c r="O14" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="P14" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="R14" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="S14" s="15">
         <v>8.8999999999999996E-2</v>
       </c>
-      <c r="S14" s="15">
+      <c r="T14" s="15">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="T14" s="15">
+      <c r="U14" s="15">
         <v>8.8999999999999996E-2</v>
       </c>
-      <c r="U14" s="15">
+      <c r="V14" s="15">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="V14" s="32">
+      <c r="W14" s="32">
         <v>2498838</v>
       </c>
-      <c r="W14" s="34">
+      <c r="X14" s="34">
         <v>222397</v>
       </c>
-      <c r="X14" s="33">
+      <c r="Y14" s="33">
         <v>444794</v>
       </c>
-      <c r="Z14" s="32">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="35"/>
-      <c r="AB14" s="32">
+      <c r="AA14" s="32">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="35"/>
+      <c r="AC14" s="32">
         <v>1487904</v>
       </c>
-      <c r="AC14" s="35"/>
-      <c r="AD14" s="32">
+      <c r="AD14" s="35"/>
+      <c r="AE14" s="32">
         <v>112324</v>
-      </c>
-      <c r="AE14" s="32">
-        <v>2045022</v>
       </c>
       <c r="AF14" s="32">
         <v>2045022</v>
       </c>
       <c r="AG14" s="32">
+        <v>2045022</v>
+      </c>
+      <c r="AH14" s="32"/>
+      <c r="AI14" s="32">
         <v>62442</v>
       </c>
-      <c r="AH14" s="32">
+      <c r="AJ14" s="32">
         <v>4152486</v>
       </c>
-      <c r="AI14" s="17"/>
-      <c r="AM14" s="24" t="s">
-        <v>199</v>
-      </c>
-      <c r="AN14" s="8" t="s">
+      <c r="AK14" s="17"/>
+      <c r="AO14" s="24" t="s">
+        <v>198</v>
+      </c>
+      <c r="AP14" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="AQ14" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="AO14" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="AP14" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="BG14" s="8">
+      <c r="AR14" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="BI14" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:87" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:89" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
         <v>14</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C15" s="31">
         <v>46100</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F15" s="41" t="s">
+        <v>262</v>
+      </c>
+      <c r="G15" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="G15" s="11" t="s">
-        <v>264</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I15" s="11" t="s">
-        <v>155</v>
+      <c r="H15" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="K15" s="11">
+        <v>154</v>
+      </c>
+      <c r="K15" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="L15" s="11">
         <v>76</v>
       </c>
-      <c r="L15" s="11" t="s">
-        <v>94</v>
-      </c>
       <c r="M15" s="11" t="s">
-        <v>137</v>
+        <v>93</v>
       </c>
       <c r="N15" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="O15" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="P15" s="27" t="s">
-        <v>296</v>
-      </c>
-      <c r="Q15" s="38" t="s">
-        <v>302</v>
-      </c>
-      <c r="R15" s="15">
+        <v>136</v>
+      </c>
+      <c r="O15" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="P15" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q15" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="R15" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="S15" s="15">
         <v>3.9E-2</v>
       </c>
-      <c r="S15" s="15">
+      <c r="T15" s="15">
         <v>1.6E-2</v>
       </c>
-      <c r="T15" s="15">
+      <c r="U15" s="15">
         <v>3.9E-2</v>
       </c>
-      <c r="U15" s="15">
+      <c r="V15" s="15">
         <v>1.6E-2</v>
       </c>
-      <c r="V15" s="32">
+      <c r="W15" s="32">
         <v>2951781</v>
       </c>
-      <c r="W15" s="34">
+      <c r="X15" s="34">
         <v>115119</v>
       </c>
-      <c r="X15" s="33">
+      <c r="Y15" s="33">
         <v>230238</v>
       </c>
-      <c r="Z15" s="32">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="35"/>
-      <c r="AB15" s="32">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="35"/>
-      <c r="AD15" s="32">
-        <v>0</v>
-      </c>
+      <c r="AA15" s="32">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="35"/>
+      <c r="AC15" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="35"/>
       <c r="AE15" s="32">
-        <v>230238</v>
+        <v>0</v>
       </c>
       <c r="AF15" s="32">
         <v>230238</v>
       </c>
       <c r="AG15" s="32">
+        <v>230238</v>
+      </c>
+      <c r="AH15" s="32"/>
+      <c r="AI15" s="32">
         <v>32322</v>
       </c>
-      <c r="AH15" s="32">
+      <c r="AJ15" s="32">
         <v>492798</v>
       </c>
-      <c r="AI15" s="51">
+      <c r="AK15" s="51">
         <v>270000</v>
       </c>
-      <c r="AJ15" s="44" t="s">
-        <v>289</v>
-      </c>
-      <c r="AK15" s="11" t="s">
-        <v>292</v>
-      </c>
-      <c r="AL15" s="27" t="s">
-        <v>295</v>
-      </c>
-      <c r="AM15" s="24" t="s">
-        <v>202</v>
-      </c>
-      <c r="AN15" s="8" t="s">
+      <c r="AL15" s="44" t="s">
+        <v>288</v>
+      </c>
+      <c r="AM15" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="AN15" s="27" t="s">
+        <v>294</v>
+      </c>
+      <c r="AO15" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="AP15" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="AQ15" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="AO15" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="AP15" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="AQ15" s="40" t="s">
-        <v>258</v>
-      </c>
-      <c r="AR15" s="40">
+      <c r="AR15" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="AS15" s="40" t="s">
+        <v>257</v>
+      </c>
+      <c r="AT15" s="40">
         <v>41</v>
       </c>
-      <c r="AS15" s="40" t="s">
+      <c r="AU15" s="40" t="s">
+        <v>259</v>
+      </c>
+      <c r="AV15" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="AW15" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="AX15" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="AT15" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="AU15" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="AV15" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="AW15" s="8">
+      <c r="AY15" s="8">
         <v>120000</v>
       </c>
-      <c r="BA15" s="11">
+      <c r="BC15" s="11">
         <v>2</v>
       </c>
-      <c r="BB15" s="11">
+      <c r="BD15" s="11">
         <v>2</v>
       </c>
-      <c r="BC15" s="11">
+      <c r="BE15" s="11">
         <v>1</v>
       </c>
-      <c r="BD15" s="11">
-        <v>0</v>
-      </c>
-      <c r="BE15" s="11">
-        <v>0</v>
-      </c>
       <c r="BF15" s="11">
+        <v>0</v>
+      </c>
+      <c r="BG15" s="11">
+        <v>0</v>
+      </c>
+      <c r="BH15" s="11">
         <v>1</v>
       </c>
-      <c r="BG15" s="11">
+      <c r="BI15" s="11">
         <v>1</v>
       </c>
-      <c r="BH15" s="54" t="s">
+      <c r="BJ15" s="54" t="s">
+        <v>283</v>
+      </c>
+      <c r="BK15" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="BL15" s="43">
+        <v>46102</v>
+      </c>
+      <c r="BM15" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="BI15" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="BJ15" s="43">
-        <v>46102</v>
-      </c>
-      <c r="BK15" s="8" t="s">
+      <c r="BN15" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="BO15" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="BL15" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="BM15" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="CG15" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="CH15" s="43">
+      <c r="CI15" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="CJ15" s="43">
         <v>46106</v>
       </c>
-      <c r="CI15" s="8">
+      <c r="CK15" s="8">
         <v>15000</v>
       </c>
     </row>
-    <row r="16" spans="1:87" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:89" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <v>15</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C16" s="31">
         <v>46100</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F16" s="41" t="s">
+        <v>262</v>
+      </c>
+      <c r="G16" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="G16" s="11" t="s">
-        <v>264</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I16" s="11" t="s">
-        <v>155</v>
+      <c r="H16" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="K16" s="11">
+        <v>154</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="L16" s="11">
         <v>76</v>
       </c>
-      <c r="L16" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="O16" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="P16" s="27" t="s">
-        <v>296</v>
-      </c>
-      <c r="Q16" s="38" t="s">
-        <v>302</v>
-      </c>
-      <c r="R16" s="15">
+      <c r="M16" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="N16" s="11"/>
+      <c r="O16" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="P16" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q16" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="R16" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="S16" s="15">
         <v>3.9E-2</v>
       </c>
-      <c r="S16" s="15">
+      <c r="T16" s="15">
         <v>1.6E-2</v>
       </c>
-      <c r="T16" s="15">
+      <c r="U16" s="15">
         <v>3.9E-2</v>
       </c>
-      <c r="U16" s="15">
+      <c r="V16" s="15">
         <v>1.6E-2</v>
       </c>
-      <c r="V16" s="32">
+      <c r="W16" s="32">
         <v>2951781</v>
       </c>
-      <c r="W16" s="34">
+      <c r="X16" s="34">
         <v>115119</v>
       </c>
-      <c r="X16" s="33">
+      <c r="Y16" s="33">
         <v>230238</v>
       </c>
-      <c r="Y16" s="8">
+      <c r="Z16" s="8">
         <v>9</v>
       </c>
-      <c r="Z16" s="32"/>
-      <c r="AA16" s="35"/>
-      <c r="AB16" s="32"/>
-      <c r="AC16" s="35"/>
-      <c r="AD16" s="32"/>
+      <c r="AA16" s="32"/>
+      <c r="AB16" s="35"/>
+      <c r="AC16" s="32"/>
+      <c r="AD16" s="35"/>
       <c r="AE16" s="32"/>
       <c r="AF16" s="32"/>
       <c r="AG16" s="32"/>
       <c r="AH16" s="32"/>
-      <c r="AI16" s="51">
+      <c r="AI16" s="32"/>
+      <c r="AJ16" s="32"/>
+      <c r="AK16" s="51">
         <v>222000</v>
       </c>
-      <c r="AJ16" s="44" t="s">
-        <v>289</v>
-      </c>
-      <c r="AK16" s="11" t="s">
-        <v>292</v>
-      </c>
-      <c r="AM16" s="24" t="s">
-        <v>203</v>
-      </c>
-      <c r="AN16" s="8" t="s">
+      <c r="AL16" s="44" t="s">
+        <v>288</v>
+      </c>
+      <c r="AM16" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="AO16" s="24" t="s">
+        <v>202</v>
+      </c>
+      <c r="AP16" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="AQ16" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="AO16" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="AP16" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="AQ16" s="40" t="s">
+      <c r="AR16" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="AS16" s="40" t="s">
+        <v>258</v>
+      </c>
+      <c r="AT16" s="40">
+        <v>38</v>
+      </c>
+      <c r="AU16" s="40" t="s">
         <v>259</v>
       </c>
-      <c r="AR16" s="40">
-        <v>38</v>
-      </c>
-      <c r="AS16" s="40" t="s">
-        <v>260</v>
-      </c>
-      <c r="AT16" s="8" t="s">
-        <v>249</v>
-      </c>
       <c r="AV16" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="AW16" s="8">
+        <v>248</v>
+      </c>
+      <c r="AX16" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="AY16" s="8">
         <v>120000</v>
       </c>
-      <c r="BA16" s="11">
+      <c r="BC16" s="11">
         <v>2</v>
       </c>
-      <c r="BB16" s="11">
+      <c r="BD16" s="11">
         <v>2</v>
       </c>
-      <c r="BC16" s="11">
+      <c r="BE16" s="11">
         <v>1</v>
       </c>
-      <c r="BD16" s="11">
-        <v>0</v>
-      </c>
-      <c r="BE16" s="11">
-        <v>0</v>
-      </c>
       <c r="BF16" s="11">
+        <v>0</v>
+      </c>
+      <c r="BG16" s="11">
+        <v>0</v>
+      </c>
+      <c r="BH16" s="11">
         <v>1</v>
       </c>
-      <c r="BG16" s="11">
-        <v>0</v>
-      </c>
-      <c r="BH16" s="54" t="s">
+      <c r="BI16" s="11">
+        <v>0</v>
+      </c>
+      <c r="BJ16" s="54" t="s">
+        <v>283</v>
+      </c>
+      <c r="BK16" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="BL16" s="43">
+        <v>46102</v>
+      </c>
+      <c r="BM16" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="BI16" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="BJ16" s="43">
-        <v>46102</v>
-      </c>
-      <c r="BK16" s="8" t="s">
+      <c r="BN16" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="BO16" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="BL16" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="BM16" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="CG16" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="CH16" s="43">
+      <c r="CI16" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="CJ16" s="43">
         <v>46106</v>
       </c>
-      <c r="CI16" s="8">
+      <c r="CK16" s="8">
         <v>15000</v>
       </c>
     </row>
-    <row r="17" spans="1:60" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:62" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <v>16</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C17" s="31">
         <v>46100</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>155</v>
+        <v>164</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="K17" s="11">
+        <v>154</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="L17" s="11">
         <v>76</v>
       </c>
-      <c r="L17" s="9">
+      <c r="M17" s="9">
         <v>46</v>
       </c>
-      <c r="M17" s="11">
+      <c r="N17" s="11">
         <v>257</v>
       </c>
-      <c r="N17" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="O17" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q17" s="38" t="s">
-        <v>302</v>
-      </c>
-      <c r="R17" s="15">
+      <c r="O17" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="P17" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="R17" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="S17" s="15">
         <v>3.9E-2</v>
       </c>
-      <c r="S17" s="15">
+      <c r="T17" s="15">
         <v>0.30399999999999999</v>
       </c>
-      <c r="T17" s="15">
+      <c r="U17" s="15">
         <v>3.9E-2</v>
       </c>
-      <c r="U17" s="15">
+      <c r="V17" s="15">
         <v>0.30399999999999999</v>
       </c>
-      <c r="V17" s="32">
+      <c r="W17" s="32">
         <v>2498838</v>
       </c>
-      <c r="W17" s="34">
+      <c r="X17" s="34">
         <v>1877127</v>
       </c>
-      <c r="X17" s="33">
+      <c r="Y17" s="33">
         <v>3754254</v>
       </c>
-      <c r="Z17" s="32">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="35"/>
-      <c r="AB17" s="32">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="35"/>
-      <c r="AD17" s="32">
-        <v>0</v>
-      </c>
+      <c r="AA17" s="32">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="35"/>
+      <c r="AC17" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="35"/>
       <c r="AE17" s="32">
-        <v>3754254</v>
+        <v>0</v>
       </c>
       <c r="AF17" s="32">
         <v>3754254</v>
       </c>
       <c r="AG17" s="32">
+        <v>3754254</v>
+      </c>
+      <c r="AH17" s="32"/>
+      <c r="AI17" s="32">
         <v>527036</v>
       </c>
-      <c r="AH17" s="32">
+      <c r="AJ17" s="32">
         <v>8035544</v>
       </c>
-      <c r="AI17" s="17"/>
-      <c r="AM17" s="24" t="s">
+      <c r="AK17" s="17"/>
+      <c r="AO17" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="AP17" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="AN17" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="AO17" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="AP17" s="8" t="s">
-        <v>204</v>
+      <c r="AQ17" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="AR17" s="8" t="s">
+        <v>203</v>
       </c>
     </row>
-    <row r="18" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
         <v>17</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C18" s="31">
         <v>46100</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I18" s="11" t="s">
-        <v>155</v>
+        <v>165</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="K18" s="11">
+        <v>154</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="L18" s="11">
         <v>76</v>
       </c>
-      <c r="L18" s="9">
+      <c r="M18" s="9">
         <v>46</v>
       </c>
-      <c r="M18" s="11">
+      <c r="N18" s="11">
         <v>316</v>
       </c>
-      <c r="N18" s="11" t="s">
-        <v>141</v>
-      </c>
       <c r="O18" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q18" s="38" t="s">
-        <v>302</v>
-      </c>
-      <c r="R18" s="15">
+        <v>140</v>
+      </c>
+      <c r="P18" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="R18" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="S18" s="15">
         <v>3.9E-2</v>
       </c>
-      <c r="S18" s="11">
+      <c r="T18" s="11">
         <v>3.3500000000000002E-2</v>
       </c>
-      <c r="T18" s="15">
+      <c r="U18" s="15">
         <v>3.9E-2</v>
       </c>
-      <c r="U18" s="11">
+      <c r="V18" s="11">
         <v>3.3500000000000002E-2</v>
       </c>
-      <c r="V18" s="32">
+      <c r="W18" s="32">
         <v>2498838</v>
       </c>
-      <c r="W18" s="34">
+      <c r="X18" s="34">
         <v>206904</v>
       </c>
-      <c r="X18" s="33">
+      <c r="Y18" s="33">
         <v>413808</v>
       </c>
-      <c r="Z18" s="32">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="35"/>
-      <c r="AB18" s="32">
-        <v>0</v>
-      </c>
-      <c r="AC18" s="35"/>
-      <c r="AD18" s="32">
-        <v>0</v>
-      </c>
+      <c r="AA18" s="32">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="35"/>
+      <c r="AC18" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="35"/>
       <c r="AE18" s="32">
-        <v>413808</v>
+        <v>0</v>
       </c>
       <c r="AF18" s="32">
         <v>413808</v>
       </c>
       <c r="AG18" s="32">
+        <v>413808</v>
+      </c>
+      <c r="AH18" s="32"/>
+      <c r="AI18" s="32">
         <v>58092</v>
       </c>
-      <c r="AH18" s="32">
+      <c r="AJ18" s="32">
         <v>885708</v>
       </c>
-      <c r="AI18" s="17"/>
-      <c r="AM18" s="24" t="s">
-        <v>213</v>
-      </c>
-      <c r="AN18" s="8" t="s">
+      <c r="AK18" s="17"/>
+      <c r="AO18" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="AP18" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="AQ18" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="AO18" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="AP18" s="8" t="s">
-        <v>205</v>
+      <c r="AR18" s="8" t="s">
+        <v>204</v>
       </c>
     </row>
-    <row r="19" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
         <v>18</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C19" s="31">
         <v>46100</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I19" s="11" t="s">
-        <v>155</v>
+        <v>166</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="K19" s="11">
+        <v>154</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="L19" s="11">
         <v>76</v>
       </c>
-      <c r="L19" s="9">
+      <c r="M19" s="9">
         <v>46</v>
       </c>
-      <c r="M19" s="11">
+      <c r="N19" s="11">
         <v>317</v>
       </c>
-      <c r="N19" s="11" t="s">
-        <v>141</v>
-      </c>
       <c r="O19" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q19" s="38" t="s">
-        <v>302</v>
-      </c>
-      <c r="R19" s="15">
+        <v>140</v>
+      </c>
+      <c r="P19" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="R19" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="S19" s="15">
         <v>3.9E-2</v>
       </c>
-      <c r="S19" s="11">
+      <c r="T19" s="11">
         <v>4.0500000000000001E-2</v>
       </c>
-      <c r="T19" s="15">
+      <c r="U19" s="15">
         <v>3.9E-2</v>
       </c>
-      <c r="U19" s="11">
+      <c r="V19" s="11">
         <v>4.0500000000000001E-2</v>
       </c>
-      <c r="V19" s="32">
+      <c r="W19" s="32">
         <v>2498838</v>
       </c>
-      <c r="W19" s="34">
+      <c r="X19" s="34">
         <v>250134</v>
       </c>
-      <c r="X19" s="33">
+      <c r="Y19" s="33">
         <v>500268</v>
       </c>
-      <c r="Z19" s="32">
-        <v>0</v>
-      </c>
-      <c r="AA19" s="35"/>
-      <c r="AB19" s="32">
-        <v>0</v>
-      </c>
-      <c r="AC19" s="35"/>
-      <c r="AD19" s="32">
-        <v>0</v>
-      </c>
+      <c r="AA19" s="32">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="35"/>
+      <c r="AC19" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="35"/>
       <c r="AE19" s="32">
-        <v>500268</v>
+        <v>0</v>
       </c>
       <c r="AF19" s="32">
         <v>500268</v>
       </c>
       <c r="AG19" s="32">
+        <v>500268</v>
+      </c>
+      <c r="AH19" s="32"/>
+      <c r="AI19" s="32">
         <v>70229</v>
       </c>
-      <c r="AH19" s="32">
+      <c r="AJ19" s="32">
         <v>1070765</v>
       </c>
-      <c r="AI19" s="17"/>
-      <c r="AM19" s="24" t="s">
-        <v>214</v>
-      </c>
-      <c r="AN19" s="8" t="s">
+      <c r="AK19" s="17"/>
+      <c r="AO19" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="AP19" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="AQ19" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="AO19" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="AP19" s="8" t="s">
-        <v>206</v>
+      <c r="AR19" s="8" t="s">
+        <v>205</v>
       </c>
     </row>
-    <row r="20" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <v>19</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C20" s="31">
         <v>46100</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I20" s="11" t="s">
-        <v>155</v>
+        <v>167</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="K20" s="11">
+        <v>154</v>
+      </c>
+      <c r="K20" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="L20" s="11">
         <v>76</v>
       </c>
-      <c r="L20" s="9">
+      <c r="M20" s="9">
         <v>46</v>
       </c>
-      <c r="M20" s="11">
+      <c r="N20" s="11">
         <v>318</v>
       </c>
-      <c r="N20" s="11" t="s">
-        <v>141</v>
-      </c>
       <c r="O20" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q20" s="38" t="s">
-        <v>302</v>
-      </c>
-      <c r="R20" s="15">
+        <v>140</v>
+      </c>
+      <c r="P20" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="R20" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="S20" s="15">
         <v>3.9E-2</v>
       </c>
-      <c r="S20" s="11">
+      <c r="T20" s="11">
         <v>4.0500000000000001E-2</v>
       </c>
-      <c r="T20" s="15">
+      <c r="U20" s="15">
         <v>3.9E-2</v>
       </c>
-      <c r="U20" s="11">
+      <c r="V20" s="11">
         <v>4.0500000000000001E-2</v>
       </c>
-      <c r="V20" s="32">
+      <c r="W20" s="32">
         <v>2498838</v>
       </c>
-      <c r="W20" s="34">
+      <c r="X20" s="34">
         <v>250134</v>
       </c>
-      <c r="X20" s="33">
+      <c r="Y20" s="33">
         <v>500268</v>
       </c>
-      <c r="Z20" s="32">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="35"/>
-      <c r="AB20" s="32">
-        <v>0</v>
-      </c>
-      <c r="AC20" s="35"/>
-      <c r="AD20" s="32">
-        <v>0</v>
-      </c>
+      <c r="AA20" s="32">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="35"/>
+      <c r="AC20" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="35"/>
       <c r="AE20" s="32">
-        <v>500268</v>
+        <v>0</v>
       </c>
       <c r="AF20" s="32">
         <v>500268</v>
       </c>
       <c r="AG20" s="32">
+        <v>500268</v>
+      </c>
+      <c r="AH20" s="32"/>
+      <c r="AI20" s="32">
         <v>70229</v>
       </c>
-      <c r="AH20" s="32">
+      <c r="AJ20" s="32">
         <v>1070765</v>
       </c>
-      <c r="AI20" s="17"/>
-      <c r="AM20" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AN20" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="AO20" s="8" t="s">
-        <v>221</v>
+      <c r="AK20" s="17"/>
+      <c r="AO20" s="24" t="s">
+        <v>214</v>
       </c>
       <c r="AP20" s="8" t="s">
-        <v>207</v>
+        <v>211</v>
+      </c>
+      <c r="AQ20" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="AR20" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
-    <row r="21" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
         <v>20</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C21" s="31">
         <v>46100</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I21" s="11" t="s">
-        <v>155</v>
+        <v>168</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="K21" s="11">
+        <v>154</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="L21" s="11">
         <v>76</v>
       </c>
-      <c r="L21" s="9">
+      <c r="M21" s="9">
         <v>46</v>
       </c>
-      <c r="M21" s="11">
+      <c r="N21" s="11">
         <v>319</v>
       </c>
-      <c r="N21" s="11" t="s">
-        <v>141</v>
-      </c>
       <c r="O21" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q21" s="38" t="s">
-        <v>302</v>
-      </c>
-      <c r="R21" s="15">
+        <v>140</v>
+      </c>
+      <c r="P21" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="R21" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="S21" s="15">
         <v>3.9E-2</v>
       </c>
-      <c r="S21" s="11">
+      <c r="T21" s="11">
         <v>4.0500000000000001E-2</v>
       </c>
-      <c r="T21" s="15">
+      <c r="U21" s="15">
         <v>3.9E-2</v>
       </c>
-      <c r="U21" s="11">
+      <c r="V21" s="11">
         <v>4.0500000000000001E-2</v>
       </c>
-      <c r="V21" s="32">
+      <c r="W21" s="32">
         <v>2498838</v>
       </c>
-      <c r="W21" s="34">
+      <c r="X21" s="34">
         <v>250134</v>
       </c>
-      <c r="X21" s="33">
+      <c r="Y21" s="33">
         <v>500268</v>
       </c>
-      <c r="Z21" s="32">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="35"/>
-      <c r="AB21" s="32">
-        <v>0</v>
-      </c>
-      <c r="AC21" s="35"/>
-      <c r="AD21" s="32">
-        <v>0</v>
-      </c>
+      <c r="AA21" s="32">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="35"/>
+      <c r="AC21" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="35"/>
       <c r="AE21" s="32">
-        <v>500268</v>
+        <v>0</v>
       </c>
       <c r="AF21" s="32">
         <v>500268</v>
       </c>
       <c r="AG21" s="32">
+        <v>500268</v>
+      </c>
+      <c r="AH21" s="32"/>
+      <c r="AI21" s="32">
         <v>70229</v>
       </c>
-      <c r="AH21" s="32">
+      <c r="AJ21" s="32">
         <v>1070765</v>
       </c>
-      <c r="AI21" s="17"/>
-      <c r="AM21" s="24" t="s">
+      <c r="AK21" s="17"/>
+      <c r="AO21" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AP21" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="AN21" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="AO21" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="AP21" s="8" t="s">
-        <v>208</v>
+      <c r="AQ21" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="AR21" s="8" t="s">
+        <v>207</v>
       </c>
     </row>
-    <row r="22" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <v>21</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C22" s="31">
         <v>46100</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>155</v>
+        <v>169</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="K22" s="11">
+        <v>154</v>
+      </c>
+      <c r="K22" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="L22" s="11">
         <v>76</v>
       </c>
-      <c r="L22" s="9">
+      <c r="M22" s="9">
         <v>46</v>
       </c>
-      <c r="M22" s="11">
+      <c r="N22" s="11">
         <v>320</v>
       </c>
-      <c r="N22" s="11" t="s">
-        <v>141</v>
-      </c>
       <c r="O22" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q22" s="38" t="s">
-        <v>302</v>
-      </c>
-      <c r="R22" s="15">
+        <v>140</v>
+      </c>
+      <c r="P22" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="R22" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="S22" s="15">
         <v>3.9E-2</v>
       </c>
-      <c r="S22" s="11">
+      <c r="T22" s="11">
         <v>5.6500000000000002E-2</v>
       </c>
-      <c r="T22" s="15">
+      <c r="U22" s="15">
         <v>3.9E-2</v>
       </c>
-      <c r="U22" s="11">
+      <c r="V22" s="11">
         <v>5.6500000000000002E-2</v>
       </c>
-      <c r="V22" s="32">
+      <c r="W22" s="32">
         <v>2498838</v>
       </c>
-      <c r="W22" s="34">
+      <c r="X22" s="34">
         <v>348838</v>
       </c>
-      <c r="X22" s="33">
+      <c r="Y22" s="33">
         <v>697676</v>
       </c>
-      <c r="Z22" s="32">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="35"/>
-      <c r="AB22" s="32">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="35"/>
-      <c r="AD22" s="32">
+      <c r="AA22" s="32">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="35"/>
+      <c r="AC22" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="35"/>
+      <c r="AE22" s="32">
         <v>325923</v>
-      </c>
-      <c r="AE22" s="32">
-        <v>1023599</v>
       </c>
       <c r="AF22" s="32">
         <v>1023599</v>
       </c>
       <c r="AG22" s="32">
+        <v>1023599</v>
+      </c>
+      <c r="AH22" s="32"/>
+      <c r="AI22" s="32">
         <v>97942</v>
       </c>
-      <c r="AH22" s="32">
+      <c r="AJ22" s="32">
         <v>2145140</v>
       </c>
-      <c r="AI22" s="17"/>
-      <c r="AM22" s="24" t="s">
+      <c r="AK22" s="17"/>
+      <c r="AO22" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="AP22" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="AN22" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="AO22" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="AP22" s="8" t="s">
-        <v>209</v>
+      <c r="AQ22" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="AR22" s="8" t="s">
+        <v>208</v>
       </c>
     </row>
-    <row r="23" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A23" s="8">
         <v>22</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C23" s="31">
         <v>46100</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I23" s="11" t="s">
-        <v>155</v>
+        <v>170</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="K23" s="11">
+        <v>154</v>
+      </c>
+      <c r="K23" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="L23" s="11">
         <v>76</v>
       </c>
-      <c r="L23" s="9">
+      <c r="M23" s="9">
         <v>46</v>
       </c>
-      <c r="M23" s="11">
+      <c r="N23" s="11">
         <v>321</v>
       </c>
-      <c r="N23" s="11" t="s">
-        <v>141</v>
-      </c>
       <c r="O23" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q23" s="38" t="s">
-        <v>302</v>
-      </c>
-      <c r="R23" s="15">
+        <v>140</v>
+      </c>
+      <c r="P23" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="R23" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="S23" s="15">
         <v>3.9E-2</v>
       </c>
-      <c r="S23" s="11">
+      <c r="T23" s="11">
         <v>0.06</v>
       </c>
-      <c r="T23" s="15">
+      <c r="U23" s="15">
         <v>3.9E-2</v>
       </c>
-      <c r="U23" s="11">
+      <c r="V23" s="11">
         <v>0.06</v>
       </c>
-      <c r="V23" s="32">
+      <c r="W23" s="32">
         <v>2498838</v>
       </c>
-      <c r="W23" s="34">
+      <c r="X23" s="34">
         <v>370578</v>
       </c>
-      <c r="X23" s="33">
+      <c r="Y23" s="33">
         <v>741156</v>
       </c>
-      <c r="Z23" s="32">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="35"/>
-      <c r="AB23" s="32">
-        <v>0</v>
-      </c>
-      <c r="AC23" s="35"/>
-      <c r="AD23" s="32">
-        <v>0</v>
-      </c>
+      <c r="AA23" s="32">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="35"/>
+      <c r="AC23" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="35"/>
       <c r="AE23" s="32">
-        <v>741156</v>
+        <v>0</v>
       </c>
       <c r="AF23" s="32">
         <v>741156</v>
       </c>
       <c r="AG23" s="32">
+        <v>741156</v>
+      </c>
+      <c r="AH23" s="32"/>
+      <c r="AI23" s="32">
         <v>104046</v>
       </c>
-      <c r="AH23" s="32">
+      <c r="AJ23" s="32">
         <v>1586358</v>
       </c>
-      <c r="AI23" s="17"/>
-      <c r="AM23" s="24" t="s">
-        <v>220</v>
-      </c>
-      <c r="AN23" s="8" t="s">
+      <c r="AK23" s="17"/>
+      <c r="AO23" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="AO23" s="8" t="s">
-        <v>223</v>
-      </c>
       <c r="AP23" s="8" t="s">
-        <v>210</v>
+        <v>218</v>
+      </c>
+      <c r="AQ23" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="AR23" s="8" t="s">
+        <v>209</v>
       </c>
     </row>
-    <row r="24" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <v>23</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C24" s="31">
         <v>46100</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I24" s="11" t="s">
-        <v>155</v>
+        <v>171</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="K24" s="11">
+        <v>154</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="L24" s="11">
         <v>76</v>
       </c>
-      <c r="L24" s="11" t="s">
-        <v>95</v>
-      </c>
       <c r="M24" s="11" t="s">
-        <v>138</v>
+        <v>94</v>
       </c>
       <c r="N24" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="O24" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q24" s="38" t="s">
-        <v>302</v>
-      </c>
-      <c r="R24" s="15">
+        <v>137</v>
+      </c>
+      <c r="O24" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="P24" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="R24" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="S24" s="15">
         <v>0.19900000000000001</v>
       </c>
-      <c r="S24" s="15">
+      <c r="T24" s="15">
         <v>8.0500000000000002E-2</v>
       </c>
-      <c r="T24" s="15">
+      <c r="U24" s="15">
         <v>0.19900000000000001</v>
       </c>
-      <c r="U24" s="15">
+      <c r="V24" s="15">
         <v>8.0500000000000002E-2</v>
       </c>
-      <c r="V24" s="32">
+      <c r="W24" s="32">
         <v>2303422</v>
       </c>
-      <c r="W24" s="34">
+      <c r="X24" s="34">
         <v>458381</v>
       </c>
-      <c r="X24" s="33">
+      <c r="Y24" s="33">
         <v>916762</v>
       </c>
-      <c r="Z24" s="32">
+      <c r="AA24" s="32">
         <v>75364</v>
       </c>
-      <c r="AA24" s="35"/>
-      <c r="AB24" s="32">
-        <v>0</v>
-      </c>
-      <c r="AC24" s="35"/>
-      <c r="AD24" s="32">
-        <v>0</v>
-      </c>
+      <c r="AB24" s="35"/>
+      <c r="AC24" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="35"/>
       <c r="AE24" s="32">
-        <v>992126</v>
+        <v>0</v>
       </c>
       <c r="AF24" s="32">
         <v>992126</v>
       </c>
       <c r="AG24" s="32">
+        <v>992126</v>
+      </c>
+      <c r="AH24" s="32"/>
+      <c r="AI24" s="32">
         <v>128698</v>
       </c>
-      <c r="AH24" s="32">
+      <c r="AJ24" s="32">
         <v>2112950</v>
       </c>
-      <c r="AI24" s="17"/>
-      <c r="AM24" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="AN24" s="8" t="s">
+      <c r="AK24" s="17"/>
+      <c r="AO24" s="24" t="s">
+        <v>224</v>
+      </c>
+      <c r="AP24" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="AQ24" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="AO24" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="AP24" s="8" t="s">
-        <v>224</v>
+      <c r="AR24" s="8" t="s">
+        <v>223</v>
       </c>
     </row>
-    <row r="25" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A25" s="8">
         <v>24</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C25" s="31">
         <v>46100</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E25" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I25" s="11" t="s">
-        <v>155</v>
+        <v>172</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="K25" s="11">
+        <v>154</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="L25" s="11">
         <v>76</v>
       </c>
-      <c r="L25" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="M25" s="11" t="s">
-        <v>139</v>
+      <c r="M25" s="9" t="s">
+        <v>95</v>
       </c>
       <c r="N25" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="O25" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q25" s="38" t="s">
-        <v>302</v>
-      </c>
-      <c r="R25" s="15">
+        <v>138</v>
+      </c>
+      <c r="O25" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="P25" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="R25" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="S25" s="15">
         <v>9.9000000000000008E-3</v>
       </c>
-      <c r="S25" s="15">
+      <c r="T25" s="15">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="T25" s="15">
+      <c r="U25" s="15">
         <v>9.9000000000000008E-3</v>
       </c>
-      <c r="U25" s="15">
+      <c r="V25" s="15">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="V25" s="32">
+      <c r="W25" s="32">
         <v>2951781</v>
       </c>
-      <c r="W25" s="34">
+      <c r="X25" s="34">
         <v>29223</v>
       </c>
-      <c r="X25" s="33">
+      <c r="Y25" s="33">
         <v>58446</v>
       </c>
-      <c r="Z25" s="32">
-        <v>0</v>
-      </c>
-      <c r="AA25" s="35"/>
-      <c r="AB25" s="32">
-        <v>0</v>
-      </c>
-      <c r="AC25" s="35"/>
-      <c r="AD25" s="32">
-        <v>0</v>
-      </c>
+      <c r="AA25" s="32">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="35"/>
+      <c r="AC25" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="35"/>
       <c r="AE25" s="32">
-        <v>58446</v>
+        <v>0</v>
       </c>
       <c r="AF25" s="32">
         <v>58446</v>
       </c>
       <c r="AG25" s="32">
+        <v>58446</v>
+      </c>
+      <c r="AH25" s="32"/>
+      <c r="AI25" s="32">
         <v>8205</v>
       </c>
-      <c r="AH25" s="32">
+      <c r="AJ25" s="32">
         <v>125097</v>
       </c>
-      <c r="AM25" s="18" t="s">
-        <v>227</v>
-      </c>
-      <c r="AN25" s="19" t="s">
+      <c r="AO25" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="AP25" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="AQ25" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="AO25" s="19" t="s">
-        <v>180</v>
-      </c>
-      <c r="AP25" s="19" t="s">
-        <v>226</v>
+      <c r="AR25" s="19" t="s">
+        <v>225</v>
       </c>
     </row>
-    <row r="26" spans="1:60" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:62" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
         <v>25</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C26" s="31">
         <v>46100</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I26" s="11" t="s">
-        <v>155</v>
+        <v>173</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="K26" s="11">
+        <v>154</v>
+      </c>
+      <c r="K26" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="L26" s="11">
         <v>76</v>
       </c>
-      <c r="L26" s="9">
+      <c r="M26" s="9">
         <v>145</v>
       </c>
-      <c r="M26" s="11">
+      <c r="N26" s="11">
         <v>166</v>
       </c>
-      <c r="N26" s="11" t="s">
-        <v>140</v>
-      </c>
       <c r="O26" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q26" s="38" t="s">
-        <v>302</v>
-      </c>
-      <c r="R26" s="15">
-        <f>ROUND(S26*2.471054,4)</f>
+        <v>139</v>
+      </c>
+      <c r="P26" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="R26" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="S26" s="15">
+        <f>ROUND(T26*2.471054,4)</f>
         <v>1.8594999999999999</v>
       </c>
-      <c r="S26" s="11">
+      <c r="T26" s="11">
         <v>0.75249999999999995</v>
       </c>
-      <c r="T26" s="15">
-        <f>ROUND(U26*2.471054,4)</f>
+      <c r="U26" s="15">
+        <f>ROUND(V26*2.471054,4)</f>
         <v>1.8594999999999999</v>
       </c>
-      <c r="U26" s="11">
+      <c r="V26" s="11">
         <v>0.75249999999999995</v>
       </c>
-      <c r="V26" s="32">
+      <c r="W26" s="32">
         <v>2498838</v>
       </c>
-      <c r="W26" s="34">
+      <c r="X26" s="34">
         <v>4646589</v>
       </c>
-      <c r="X26" s="33">
+      <c r="Y26" s="33">
         <v>9293178</v>
       </c>
-      <c r="Z26" s="32">
-        <v>0</v>
-      </c>
-      <c r="AA26" s="35"/>
-      <c r="AB26" s="32">
-        <v>0</v>
-      </c>
-      <c r="AC26" s="35"/>
-      <c r="AD26" s="32">
-        <v>0</v>
-      </c>
+      <c r="AA26" s="32">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="35"/>
+      <c r="AC26" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="35"/>
       <c r="AE26" s="32">
-        <v>9293178</v>
+        <v>0</v>
       </c>
       <c r="AF26" s="32">
         <v>9293178</v>
       </c>
       <c r="AG26" s="32">
+        <v>9293178</v>
+      </c>
+      <c r="AH26" s="32"/>
+      <c r="AI26" s="32">
         <v>1304609</v>
       </c>
-      <c r="AH26" s="32">
+      <c r="AJ26" s="32">
         <v>19890965</v>
       </c>
-      <c r="AM26" s="24" t="s">
-        <v>231</v>
-      </c>
-      <c r="AN26" s="8" t="s">
+      <c r="AO26" s="24" t="s">
+        <v>230</v>
+      </c>
+      <c r="AP26" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="AQ26" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="AO26" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="AP26" s="8" t="s">
-        <v>228</v>
+      <c r="AR26" s="8" t="s">
+        <v>227</v>
       </c>
     </row>
-    <row r="27" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A27" s="8">
         <v>26</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C27" s="31">
         <v>46100</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I27" s="11" t="s">
-        <v>155</v>
+        <v>174</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="K27" s="11">
+        <v>154</v>
+      </c>
+      <c r="K27" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="L27" s="11">
         <v>76</v>
       </c>
-      <c r="L27" s="9">
+      <c r="M27" s="9">
         <v>145</v>
       </c>
-      <c r="M27" s="11"/>
       <c r="N27" s="11"/>
       <c r="O27" s="11"/>
-      <c r="Q27" s="38" t="s">
-        <v>302</v>
-      </c>
-      <c r="R27" s="15">
-        <f>ROUND(S27*2.471054,4)</f>
+      <c r="P27" s="11"/>
+      <c r="R27" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="S27" s="15">
+        <f>ROUND(T27*2.471054,4)</f>
         <v>0.69440000000000002</v>
       </c>
-      <c r="S27" s="11">
+      <c r="T27" s="11">
         <v>0.28100000000000003</v>
       </c>
-      <c r="T27" s="15">
-        <f>ROUND(U27*2.471054,4)</f>
+      <c r="U27" s="15">
+        <f>ROUND(V27*2.471054,4)</f>
         <v>0.69440000000000002</v>
       </c>
-      <c r="U27" s="11">
+      <c r="V27" s="11">
         <v>0.28100000000000003</v>
       </c>
-      <c r="V27" s="32">
+      <c r="W27" s="32">
         <v>2498838</v>
       </c>
-      <c r="W27" s="34">
+      <c r="X27" s="34">
         <v>1735193</v>
       </c>
-      <c r="X27" s="33">
+      <c r="Y27" s="33">
         <v>3470386</v>
       </c>
-      <c r="Z27" s="32"/>
-      <c r="AA27" s="35"/>
-      <c r="AB27" s="32"/>
-      <c r="AC27" s="35"/>
-      <c r="AD27" s="32"/>
+      <c r="AA27" s="32"/>
+      <c r="AB27" s="35"/>
+      <c r="AC27" s="32"/>
+      <c r="AD27" s="35"/>
       <c r="AE27" s="32"/>
       <c r="AF27" s="32"/>
       <c r="AG27" s="32"/>
       <c r="AH27" s="32"/>
-      <c r="AM27" s="24" t="s">
-        <v>232</v>
-      </c>
-      <c r="AN27" s="8" t="s">
+      <c r="AI27" s="32"/>
+      <c r="AJ27" s="32"/>
+      <c r="AO27" s="24" t="s">
+        <v>231</v>
+      </c>
+      <c r="AP27" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="AQ27" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="AO27" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="AP27" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="BH27" s="40" t="s">
-        <v>277</v>
+      <c r="AR27" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="BJ27" s="40" t="s">
+        <v>276</v>
       </c>
     </row>
-    <row r="28" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
         <v>27</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C28" s="31">
         <v>46100</v>
       </c>
       <c r="D28" s="20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I28" s="11" t="s">
-        <v>155</v>
+        <v>156</v>
+      </c>
+      <c r="H28" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="K28" s="11">
+        <v>154</v>
+      </c>
+      <c r="K28" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="L28" s="11">
         <v>76</v>
       </c>
-      <c r="L28" s="9">
+      <c r="M28" s="9">
         <v>145</v>
       </c>
-      <c r="M28" s="11">
+      <c r="N28" s="11">
         <v>200</v>
       </c>
-      <c r="N28" s="11" t="s">
-        <v>140</v>
-      </c>
       <c r="O28" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q28" s="38" t="s">
-        <v>302</v>
-      </c>
-      <c r="R28" s="29"/>
-      <c r="S28" s="11"/>
-      <c r="T28" s="29"/>
-      <c r="U28" s="11"/>
-      <c r="V28" s="7"/>
-      <c r="W28" s="34"/>
-      <c r="X28" s="33"/>
-      <c r="Z28" s="32">
-        <v>0</v>
-      </c>
-      <c r="AA28" s="35"/>
-      <c r="AB28" s="32">
-        <v>0</v>
-      </c>
-      <c r="AC28" s="35"/>
-      <c r="AD28" s="32">
-        <v>0</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="P28" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="R28" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="S28" s="29"/>
+      <c r="T28" s="11"/>
+      <c r="U28" s="29"/>
+      <c r="V28" s="11"/>
+      <c r="W28" s="7"/>
+      <c r="X28" s="34"/>
+      <c r="Y28" s="33"/>
+      <c r="AA28" s="32">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="35"/>
+      <c r="AC28" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="35"/>
       <c r="AE28" s="32">
-        <v>3470386</v>
+        <v>0</v>
       </c>
       <c r="AF28" s="32">
         <v>3470386</v>
       </c>
       <c r="AG28" s="32">
+        <v>3470386</v>
+      </c>
+      <c r="AH28" s="32"/>
+      <c r="AI28" s="32">
         <v>487185</v>
       </c>
-      <c r="AH28" s="32">
+      <c r="AJ28" s="32">
         <v>7427957</v>
       </c>
-      <c r="AM28" s="24" t="s">
-        <v>233</v>
-      </c>
-      <c r="AN28" s="8" t="s">
+      <c r="AO28" s="24" t="s">
+        <v>232</v>
+      </c>
+      <c r="AP28" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="AQ28" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="AO28" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="AP28" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="BH28" s="40" t="s">
-        <v>277</v>
+      <c r="AR28" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="BJ28" s="40" t="s">
+        <v>276</v>
       </c>
     </row>
-    <row r="29" spans="1:60" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:62" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="8">
         <v>28</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C29" s="31">
         <v>46100</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I29" s="11" t="s">
-        <v>155</v>
+        <v>175</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="K29" s="11">
+        <v>154</v>
+      </c>
+      <c r="K29" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="L29" s="11">
         <v>76</v>
       </c>
-      <c r="L29" s="9">
+      <c r="M29" s="9">
         <v>336</v>
       </c>
-      <c r="M29" s="11">
+      <c r="N29" s="11">
         <v>115</v>
       </c>
-      <c r="N29" s="11" t="s">
-        <v>87</v>
-      </c>
       <c r="O29" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q29" s="38" t="s">
-        <v>302</v>
-      </c>
-      <c r="R29" s="29"/>
-      <c r="S29" s="11">
+        <v>86</v>
+      </c>
+      <c r="P29" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="R29" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="S29" s="29"/>
+      <c r="T29" s="11">
         <v>0.13600000000000001</v>
       </c>
-      <c r="T29" s="29"/>
-      <c r="U29" s="11">
+      <c r="U29" s="29"/>
+      <c r="V29" s="11">
         <v>0.13600000000000001</v>
       </c>
-      <c r="V29" s="7" t="s">
+      <c r="W29" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="X29" s="34" t="s">
         <v>151</v>
       </c>
-      <c r="W29" s="34" t="s">
-        <v>152</v>
-      </c>
-      <c r="X29" s="33">
+      <c r="Y29" s="33">
         <v>1548360</v>
       </c>
-      <c r="Z29" s="32">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="35"/>
-      <c r="AB29" s="32">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="35"/>
-      <c r="AD29" s="32">
-        <v>0</v>
-      </c>
+      <c r="AA29" s="32">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="35"/>
+      <c r="AC29" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="35"/>
       <c r="AE29" s="32">
-        <v>1548360</v>
+        <v>0</v>
       </c>
       <c r="AF29" s="32">
         <v>1548360</v>
       </c>
       <c r="AG29" s="32">
+        <v>1548360</v>
+      </c>
+      <c r="AH29" s="32"/>
+      <c r="AI29" s="32">
         <v>217364</v>
       </c>
-      <c r="AH29" s="32">
+      <c r="AJ29" s="32">
         <v>3314084</v>
       </c>
-      <c r="AM29" s="24" t="s">
-        <v>236</v>
-      </c>
-      <c r="AN29" s="11" t="s">
+      <c r="AO29" s="24" t="s">
+        <v>235</v>
+      </c>
+      <c r="AP29" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="AQ29" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="AO29" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="AP29" s="8" t="s">
-        <v>234</v>
+      <c r="AR29" s="8" t="s">
+        <v>233</v>
       </c>
     </row>
-    <row r="30" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A30" s="8">
         <v>29</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C30" s="31">
         <v>46100</v>
       </c>
       <c r="D30" s="20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I30" s="11" t="s">
-        <v>155</v>
+        <v>176</v>
+      </c>
+      <c r="H30" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="K30" s="11">
+        <v>154</v>
+      </c>
+      <c r="K30" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="L30" s="11">
         <v>76</v>
       </c>
-      <c r="L30" s="9">
+      <c r="M30" s="9">
         <v>336</v>
       </c>
-      <c r="M30" s="11">
+      <c r="N30" s="11">
         <v>116</v>
       </c>
-      <c r="N30" s="11" t="s">
-        <v>140</v>
-      </c>
       <c r="O30" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q30" s="38" t="s">
-        <v>303</v>
-      </c>
-      <c r="R30" s="29"/>
-      <c r="S30" s="11">
+        <v>139</v>
+      </c>
+      <c r="P30" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="R30" s="38" t="s">
+        <v>300</v>
+      </c>
+      <c r="S30" s="29"/>
+      <c r="T30" s="11">
         <v>0.82850000000000001</v>
       </c>
-      <c r="T30" s="29"/>
-      <c r="U30" s="11">
+      <c r="U30" s="29"/>
+      <c r="V30" s="11">
         <v>0.82850000000000001</v>
       </c>
-      <c r="V30" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="W30" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="X30" s="33">
+      <c r="W30" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="X30" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y30" s="33">
         <v>10231742</v>
       </c>
-      <c r="Z30" s="32">
+      <c r="AA30" s="32">
         <v>1255840</v>
       </c>
-      <c r="AA30" s="35"/>
-      <c r="AB30" s="32">
-        <v>0</v>
-      </c>
-      <c r="AC30" s="35"/>
-      <c r="AD30" s="32">
-        <v>0</v>
-      </c>
+      <c r="AB30" s="35"/>
+      <c r="AC30" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="35"/>
       <c r="AE30" s="32">
-        <v>11487582</v>
+        <v>0</v>
       </c>
       <c r="AF30" s="32">
         <v>11487582</v>
       </c>
       <c r="AG30" s="32">
+        <v>11487582</v>
+      </c>
+      <c r="AH30" s="32"/>
+      <c r="AI30" s="32">
         <v>1436368</v>
       </c>
-      <c r="AH30" s="32">
+      <c r="AJ30" s="32">
         <v>24411532</v>
       </c>
-      <c r="AM30" s="24" t="s">
-        <v>237</v>
-      </c>
-      <c r="AN30" s="8" t="s">
+      <c r="AO30" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="AP30" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="AQ30" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="AO30" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="AP30" s="8" t="s">
-        <v>235</v>
+      <c r="AR30" s="8" t="s">
+        <v>234</v>
       </c>
     </row>
-    <row r="31" spans="1:60" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:62" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="8">
         <v>30</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C31" s="31">
         <v>46100</v>
       </c>
       <c r="D31" s="23" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I31" s="11" t="s">
-        <v>155</v>
+        <v>109</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="K31" s="11">
+        <v>154</v>
+      </c>
+      <c r="K31" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="L31" s="11">
         <v>76</v>
       </c>
-      <c r="L31" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="M31" s="11">
+      <c r="M31" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="N31" s="11">
         <v>74</v>
       </c>
-      <c r="N31" s="11" t="s">
-        <v>144</v>
-      </c>
       <c r="O31" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q31" s="38" t="s">
-        <v>302</v>
-      </c>
-      <c r="R31" s="15">
+        <v>143</v>
+      </c>
+      <c r="P31" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="R31" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="S31" s="15">
         <v>0.1038</v>
       </c>
-      <c r="S31" s="11">
+      <c r="T31" s="11">
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="T31" s="15">
+      <c r="U31" s="15">
         <v>0.1038</v>
       </c>
-      <c r="U31" s="11">
+      <c r="V31" s="11">
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="V31" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="W31" s="34" t="s">
-        <v>153</v>
-      </c>
-      <c r="X31" s="33">
+      <c r="W31" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="X31" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="Y31" s="33">
         <v>526560</v>
       </c>
-      <c r="Z31" s="32">
-        <v>0</v>
-      </c>
-      <c r="AA31" s="35"/>
-      <c r="AB31" s="32">
-        <v>0</v>
-      </c>
-      <c r="AC31" s="35"/>
-      <c r="AD31" s="32">
-        <v>0</v>
-      </c>
+      <c r="AA31" s="32">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="35"/>
+      <c r="AC31" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="35"/>
       <c r="AE31" s="32">
-        <v>526560</v>
+        <v>0</v>
       </c>
       <c r="AF31" s="32">
         <v>526560</v>
       </c>
       <c r="AG31" s="32">
+        <v>526560</v>
+      </c>
+      <c r="AH31" s="32"/>
+      <c r="AI31" s="32">
         <v>73920</v>
       </c>
-      <c r="AH31" s="32">
+      <c r="AJ31" s="32">
         <v>1127040</v>
       </c>
-      <c r="AM31" s="24" t="s">
+      <c r="AO31" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="AP31" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="AQ31" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="AN31" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="AO31" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="AP31" s="8" t="s">
-        <v>238</v>
+      <c r="AR31" s="8" t="s">
+        <v>237</v>
       </c>
     </row>
-    <row r="32" spans="1:60" ht="110.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:62" ht="110.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
         <v>31</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D32" s="23" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F32" s="23"/>
       <c r="G32" s="23"/>
-      <c r="H32" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="I32" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="J32" s="23" t="s">
-        <v>243</v>
-      </c>
-      <c r="K32" s="23">
+      <c r="H32" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="J32" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="K32" s="23" t="s">
+        <v>242</v>
+      </c>
+      <c r="L32" s="23">
         <v>75</v>
       </c>
-      <c r="L32" s="11">
+      <c r="M32" s="11">
         <v>652</v>
       </c>
-      <c r="M32" s="11">
+      <c r="N32" s="11">
         <v>4504</v>
       </c>
-      <c r="N32" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="O32" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="P32" s="23"/>
-      <c r="Q32" s="38" t="s">
-        <v>302</v>
-      </c>
-      <c r="R32" s="15">
+      <c r="O32" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="P32" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q32" s="23"/>
+      <c r="R32" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="S32" s="15">
         <v>0.48930000000000001</v>
       </c>
-      <c r="S32" s="15">
+      <c r="T32" s="15">
         <v>0.19800000000000001</v>
       </c>
-      <c r="T32" s="15">
+      <c r="U32" s="15">
         <v>0.48930000000000001</v>
       </c>
-      <c r="U32" s="15">
+      <c r="V32" s="15">
         <v>0.19800000000000001</v>
       </c>
-      <c r="V32" s="23"/>
       <c r="W32" s="23"/>
       <c r="X32" s="23"/>
       <c r="Y32" s="23"/>
-      <c r="Z32" s="36"/>
-      <c r="AA32" s="35"/>
+      <c r="Z32" s="23"/>
+      <c r="AA32" s="36"/>
       <c r="AB32" s="35"/>
       <c r="AC32" s="35"/>
       <c r="AD32" s="35"/>
@@ -5942,23 +6088,25 @@
       <c r="AF32" s="35"/>
       <c r="AG32" s="35"/>
       <c r="AH32" s="35"/>
+      <c r="AI32" s="35"/>
+      <c r="AJ32" s="35"/>
     </row>
-    <row r="33" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q33" s="38"/>
+    <row r="33" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R33" s="38"/>
     </row>
-    <row r="34" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q34" s="38"/>
+    <row r="34" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R34" s="38"/>
     </row>
-    <row r="35" spans="17:17" x14ac:dyDescent="0.25">
-      <c r="Q35" s="38"/>
+    <row r="35" spans="18:18" x14ac:dyDescent="0.25">
+      <c r="R35" s="38"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="L1">
+  <conditionalFormatting sqref="M1">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q21:Q28 Q2:Q14" xr:uid="{24D911A6-D502-4CEA-8117-E68B46B3AEB9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R21:R28 R2:R14" xr:uid="{24D911A6-D502-4CEA-8117-E68B46B3AEB9}">
       <formula1>"Full,Part,N.A."</formula1>
     </dataValidation>
   </dataValidations>
